--- a/database/event/2569/event_2569_evp_summary.xlsx
+++ b/database/event/2569/event_2569_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4312</v>
+        <v>5.4432</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3041</v>
+        <v>1.307</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7727</v>
+        <v>1.7247</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4312</v>
+        <v>5.4432</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0195</v>
+        <v>3.0315</v>
       </c>
       <c r="G2" t="n">
         <v>2.4117</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0195</v>
+        <v>3.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4474</v>
+        <v>2.4571</v>
       </c>
       <c r="J2" t="n">
         <v>2.4117</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8591</v>
+        <v>4.8688</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.7101</v>
+        <v>4.8527</v>
       </c>
       <c r="C3" t="n">
-        <v>1.131</v>
+        <v>1.1652</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4814</v>
+        <v>1.4894</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7101</v>
+        <v>4.8527</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4974</v>
+        <v>3.64</v>
       </c>
       <c r="G3" t="n">
         <v>1.2127</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4974</v>
+        <v>3.64</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8347</v>
+        <v>2.9503</v>
       </c>
       <c r="J3" t="n">
         <v>1.2127</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>4.0474</v>
+        <v>4.163</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -594,7 +594,7 @@
         <v>0.9136</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1157</v>
+        <v>1.072</v>
       </c>
       <c r="E4" t="n">
         <v>3.8049</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6846</v>
+        <v>3.6891</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8847</v>
+        <v>0.8858</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0671</v>
+        <v>1.0258</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6846</v>
+        <v>3.6891</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2282</v>
+        <v>1.2327</v>
       </c>
       <c r="G5" t="n">
         <v>2.4564</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2282</v>
+        <v>1.2327</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="J5" t="n">
         <v>2.4564</v>
@@ -667,7 +667,7 @@
         <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4519</v>
+        <v>3.4555</v>
       </c>
       <c r="N5" t="n">
         <v>290</v>
@@ -686,7 +686,7 @@
         <v>0.8506</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0098</v>
+        <v>0.9675</v>
       </c>
       <c r="E6" t="n">
         <v>3.5426</v>
@@ -722,461 +722,461 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7458</v>
+        <v>3.0182</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6593</v>
+        <v>0.7247</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6879</v>
+        <v>0.7585</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7458</v>
+        <v>3.0182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.854</v>
+        <v>1.8159</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8918</v>
+        <v>1.2023</v>
       </c>
       <c r="H7" t="n">
-        <v>0.854</v>
+        <v>1.8159</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6922</v>
+        <v>1.4718</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8918</v>
+        <v>1.2023</v>
       </c>
       <c r="K7" t="n">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="L7" t="n">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.584</v>
+        <v>2.6741</v>
       </c>
       <c r="N7" t="n">
-        <v>290</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7162</v>
+        <v>2.7458</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6522</v>
+        <v>0.6593</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7162</v>
+        <v>2.7458</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5139</v>
+        <v>0.854</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2023</v>
+        <v>1.8918</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5139</v>
+        <v>0.854</v>
       </c>
       <c r="I8" t="n">
-        <v>1.227</v>
+        <v>0.6922</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2023</v>
+        <v>1.8918</v>
       </c>
       <c r="K8" t="n">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="L8" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4293</v>
+        <v>2.584</v>
       </c>
       <c r="N8" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4555</v>
+        <v>2.5988</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5896</v>
+        <v>0.624</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5706</v>
+        <v>0.5915</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4555</v>
+        <v>2.5988</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4555</v>
+        <v>3.5988</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4555</v>
+        <v>3.5988</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4555</v>
+        <v>2.9169</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K9" t="n">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4555</v>
+        <v>1.9169</v>
       </c>
       <c r="N9" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3829</v>
+        <v>2.4555</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5722</v>
+        <v>0.5896</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5413</v>
+        <v>0.5344</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3829</v>
+        <v>2.4555</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5805</v>
+        <v>2.4555</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8025</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5805</v>
+        <v>2.4555</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4705</v>
+        <v>2.4555</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8025</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L10" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.273</v>
+        <v>2.4555</v>
       </c>
       <c r="N10" t="n">
-        <v>290</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3027</v>
+        <v>2.4487</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5089</v>
+        <v>0.5317</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3027</v>
+        <v>2.4487</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3027</v>
+        <v>0.6462</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.8025</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3027</v>
+        <v>0.6462</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3027</v>
+        <v>0.5238</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.8025</v>
       </c>
       <c r="K11" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3027</v>
+        <v>2.3263</v>
       </c>
       <c r="N11" t="n">
-        <v>154</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1868</v>
+        <v>2.3027</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5251</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4621</v>
+        <v>0.4735</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1868</v>
+        <v>2.3027</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2092</v>
+        <v>2.3027</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9776</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2092</v>
+        <v>2.3027</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1696</v>
+        <v>2.3027</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9776</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="L12" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1472</v>
+        <v>2.3027</v>
       </c>
       <c r="N12" t="n">
-        <v>247</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8306</v>
+        <v>2.1868</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4396</v>
+        <v>0.5251</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3182</v>
+        <v>0.4273</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8306</v>
+        <v>2.1868</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8306</v>
+        <v>0.2092</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.9776</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8306</v>
+        <v>0.2092</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8306</v>
+        <v>0.1696</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.9776</v>
       </c>
       <c r="K13" t="n">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8306</v>
+        <v>2.1472</v>
       </c>
       <c r="N13" t="n">
-        <v>154</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.72</v>
+        <v>1.8306</v>
       </c>
       <c r="C14" t="n">
-        <v>0.413</v>
+        <v>0.4396</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2735</v>
+        <v>0.2854</v>
       </c>
       <c r="E14" t="n">
-        <v>1.72</v>
+        <v>1.8306</v>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>1.8306</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>1.8306</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2046</v>
+        <v>1.8306</v>
       </c>
       <c r="J14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="L14" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2046</v>
+        <v>1.8306</v>
       </c>
       <c r="N14" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4467</v>
+        <v>1.4483</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3474</v>
+        <v>0.3478</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1631</v>
+        <v>0.1331</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4467</v>
+        <v>1.4483</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4467</v>
+        <v>2.0944</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.6461</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4467</v>
+        <v>2.0944</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4467</v>
+        <v>1.6976</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.6461</v>
       </c>
       <c r="K15" t="n">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4467</v>
+        <v>1.0515</v>
       </c>
       <c r="N15" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1391</v>
+        <v>1.4467</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2735</v>
+        <v>0.3474</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0388</v>
+        <v>0.1325</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1391</v>
+        <v>1.4467</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7852</v>
+        <v>1.4467</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6461</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7852</v>
+        <v>1.4467</v>
       </c>
       <c r="I16" t="n">
-        <v>1.447</v>
+        <v>1.4467</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6461</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="L16" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8009000000000001</v>
+        <v>1.4467</v>
       </c>
       <c r="N16" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
@@ -1192,7 +1192,7 @@
         <v>0.2561</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0094</v>
+        <v>-0.0191</v>
       </c>
       <c r="E17" t="n">
         <v>1.0664</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8757</v>
+        <v>0.9232</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2103</v>
+        <v>0.2217</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0761</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8757</v>
+        <v>0.9232</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8757</v>
+        <v>1.9232</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8757</v>
+        <v>1.9232</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8757</v>
+        <v>1.5588</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8757</v>
+        <v>0.5588</v>
       </c>
       <c r="N18" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8329</v>
+        <v>0.885</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2</v>
+        <v>0.2125</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0849</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8329</v>
+        <v>0.885</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6879</v>
+        <v>0.74</v>
       </c>
       <c r="G19" t="n">
         <v>0.145</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6879</v>
+        <v>0.74</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5576</v>
+        <v>0.5998</v>
       </c>
       <c r="J19" t="n">
         <v>0.145</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7026</v>
+        <v>0.7448</v>
       </c>
       <c r="N19" t="n">
         <v>247</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7915</v>
+        <v>0.8757</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1901</v>
+        <v>0.2103</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1016</v>
+        <v>-0.095</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7915</v>
+        <v>0.8757</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7915</v>
+        <v>0.8757</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7915</v>
+        <v>0.8757</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4521</v>
+        <v>0.8757</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="L20" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4520999999999999</v>
+        <v>0.8757</v>
       </c>
       <c r="N20" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -1376,7 +1376,7 @@
         <v>0.1594</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1532</v>
+        <v>-0.1794</v>
       </c>
       <c r="E21" t="n">
         <v>0.6639</v>
@@ -1412,35 +1412,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4068</v>
+        <v>0.5454</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0977</v>
+        <v>0.131</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.257</v>
+        <v>-0.2266</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4068</v>
+        <v>0.5454</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1479</v>
+        <v>1.0472</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2589</v>
+        <v>-0.5018</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1479</v>
+        <v>1.0472</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1199</v>
+        <v>0.8488</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2589</v>
+        <v>-0.5018</v>
       </c>
       <c r="K22" t="n">
         <v>48</v>
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3788</v>
+        <v>0.347</v>
       </c>
       <c r="N22" t="n">
         <v>119</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3831</v>
+        <v>0.4068</v>
       </c>
       <c r="C23" t="n">
-        <v>0.092</v>
+        <v>0.0977</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2666</v>
+        <v>-0.2818</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3831</v>
+        <v>0.4068</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3831</v>
+        <v>0.1479</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.2589</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3831</v>
+        <v>0.1479</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3831</v>
+        <v>0.1199</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.2589</v>
       </c>
       <c r="K23" t="n">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3831</v>
+        <v>0.3788</v>
       </c>
       <c r="N23" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3672</v>
+        <v>0.3831</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0882</v>
+        <v>0.092</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.273</v>
+        <v>-0.2913</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3672</v>
+        <v>0.3831</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3672</v>
+        <v>0.3831</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3672</v>
+        <v>0.3831</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3672</v>
+        <v>0.3831</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3672</v>
+        <v>0.3831</v>
       </c>
       <c r="N24" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3408</v>
+        <v>0.3672</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0818</v>
+        <v>0.0882</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2837</v>
+        <v>-0.2976</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3408</v>
+        <v>0.3672</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8426</v>
+        <v>0.3672</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5018</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8426</v>
+        <v>0.3672</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6829</v>
+        <v>0.3672</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5018</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="L25" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1810999999999999</v>
+        <v>0.3672</v>
       </c>
       <c r="N25" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
@@ -1606,7 +1606,7 @@
         <v>0.0538</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3308</v>
+        <v>-0.3546</v>
       </c>
       <c r="E26" t="n">
         <v>0.2242</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0281</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4686</v>
+        <v>-0.4905</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1169</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0848</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5641</v>
+        <v>-0.5847</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3533</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0985</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.587</v>
+        <v>-0.6073</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4101</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1091</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6048</v>
+        <v>-0.6249</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4542</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1162</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6169</v>
+        <v>-0.6367</v>
       </c>
       <c r="E31" t="n">
         <v>-0.484</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1363</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6506</v>
+        <v>-0.67</v>
       </c>
       <c r="E32" t="n">
         <v>-0.5675</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1508</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6751</v>
+        <v>-0.6942</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6282</v>
@@ -1974,7 +1974,7 @@
         <v>-0.151</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6754</v>
+        <v>-0.6944</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6288</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2188</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7895</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9114</v>
@@ -2066,7 +2066,7 @@
         <v>-0.235</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8167</v>
+        <v>-0.8338</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9786</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0351</v>
+        <v>-0.9958</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2485</v>
+        <v>-0.2391</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8395</v>
+        <v>-0.8406</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0351</v>
+        <v>-0.9958</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0722</v>
+        <v>-1.0329</v>
       </c>
       <c r="G37" t="n">
         <v>0.0371</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0722</v>
+        <v>-1.0329</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.869</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0.0371</v>
@@ -2139,7 +2139,7 @@
         <v>139</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8319</v>
+        <v>-0.8001</v>
       </c>
       <c r="N37" t="n">
         <v>290</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2761</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8858</v>
+        <v>-0.902</v>
       </c>
       <c r="E38" t="n">
         <v>-1.1497</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3094</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9419</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="E39" t="n">
         <v>-1.2885</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3125</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9624</v>
       </c>
       <c r="E40" t="n">
         <v>-1.3015</v>
@@ -2296,7 +2296,7 @@
         <v>-0.3813</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0628</v>
+        <v>-1.0765</v>
       </c>
       <c r="E41" t="n">
         <v>-1.5879</v>

--- a/database/event/2569/event_2569_evp_summary.xlsx
+++ b/database/event/2569/event_2569_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4432</v>
+        <v>5.4274</v>
       </c>
       <c r="C2" t="n">
-        <v>1.307</v>
+        <v>1.3032</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7247</v>
+        <v>1.8122</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4432</v>
+        <v>5.4274</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0315</v>
+        <v>3.0106</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4117</v>
+        <v>2.4168</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0315</v>
+        <v>5.121</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4571</v>
+        <v>2.6627</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4117</v>
+        <v>2.4168</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8688</v>
+        <v>5.079499999999999</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8527</v>
+        <v>4.6109</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1652</v>
+        <v>1.1072</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4894</v>
+        <v>1.4436</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8527</v>
+        <v>4.6109</v>
       </c>
       <c r="F3" t="n">
-        <v>3.64</v>
+        <v>1.9733</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2127</v>
+        <v>2.6376</v>
       </c>
       <c r="H3" t="n">
-        <v>3.64</v>
+        <v>1.9733</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9503</v>
+        <v>1.026</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2127</v>
+        <v>2.6376</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>4.163</v>
+        <v>3.6636</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8049</v>
+        <v>4.5661</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9136</v>
+        <v>1.0964</v>
       </c>
       <c r="D4" t="n">
-        <v>1.072</v>
+        <v>1.4234</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8049</v>
+        <v>4.5661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7788</v>
+        <v>3.2426</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0262</v>
+        <v>1.3235</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7788</v>
+        <v>5.9386</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6312</v>
+        <v>3.0878</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0262</v>
+        <v>1.3235</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -621,7 +621,7 @@
         <v>141</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6574</v>
+        <v>4.4113</v>
       </c>
       <c r="N4" t="n">
         <v>247</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6891</v>
+        <v>4.0485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8858</v>
+        <v>0.9721</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0258</v>
+        <v>1.1897</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6891</v>
+        <v>4.0485</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2327</v>
+        <v>1.9669</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4564</v>
+        <v>2.0816</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2327</v>
+        <v>1.9669</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9991</v>
+        <v>1.0227</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4564</v>
+        <v>2.0816</v>
       </c>
       <c r="K5" t="n">
         <v>151</v>
@@ -667,7 +667,7 @@
         <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4555</v>
+        <v>3.1043</v>
       </c>
       <c r="N5" t="n">
         <v>290</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5426</v>
+        <v>3.9943</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8506</v>
+        <v>0.9591</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9675</v>
+        <v>1.1652</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5426</v>
+        <v>3.9943</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0589</v>
+        <v>1.6688</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4837</v>
+        <v>2.3255</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0589</v>
+        <v>1.6688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8583</v>
+        <v>0.8677</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4837</v>
+        <v>2.3255</v>
       </c>
       <c r="K6" t="n">
         <v>151</v>
@@ -713,7 +713,7 @@
         <v>139</v>
       </c>
       <c r="M6" t="n">
-        <v>3.342</v>
+        <v>3.1932</v>
       </c>
       <c r="N6" t="n">
         <v>290</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0182</v>
+        <v>3.3154</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7247</v>
+        <v>0.7961</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7585</v>
+        <v>0.8587</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0182</v>
+        <v>3.3154</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8159</v>
+        <v>2.3339</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2023</v>
+        <v>0.9815</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8159</v>
+        <v>2.737</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4718</v>
+        <v>1.4231</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2023</v>
+        <v>0.9815</v>
       </c>
       <c r="K7" t="n">
         <v>94</v>
@@ -759,7 +759,7 @@
         <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6741</v>
+        <v>2.4046</v>
       </c>
       <c r="N7" t="n">
         <v>167</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7458</v>
+        <v>3.2721</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6593</v>
+        <v>0.7857</v>
       </c>
       <c r="D8" t="n">
-        <v>0.65</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7458</v>
+        <v>3.2721</v>
       </c>
       <c r="F8" t="n">
-        <v>0.854</v>
+        <v>1.3563</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8918</v>
+        <v>1.9158</v>
       </c>
       <c r="H8" t="n">
-        <v>0.854</v>
+        <v>1.3563</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6922</v>
+        <v>0.7052</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8918</v>
+        <v>1.9158</v>
       </c>
       <c r="K8" t="n">
         <v>151</v>
@@ -805,7 +805,7 @@
         <v>139</v>
       </c>
       <c r="M8" t="n">
-        <v>2.584</v>
+        <v>2.621</v>
       </c>
       <c r="N8" t="n">
         <v>290</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5988</v>
+        <v>2.8461</v>
       </c>
       <c r="C9" t="n">
-        <v>0.624</v>
+        <v>0.6834</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5915</v>
+        <v>0.6469</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5988</v>
+        <v>2.8461</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5988</v>
+        <v>1.2667</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>1.5794</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5988</v>
+        <v>1.2667</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9169</v>
+        <v>0.6586</v>
       </c>
       <c r="J9" t="n">
-        <v>-1</v>
+        <v>1.5794</v>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="L9" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9169</v>
+        <v>2.238</v>
       </c>
       <c r="N9" t="n">
-        <v>119</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4555</v>
+        <v>2.7945</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5896</v>
+        <v>0.671</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5344</v>
+        <v>0.6236</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4555</v>
+        <v>2.7945</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4555</v>
+        <v>1.0222</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.7723</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4555</v>
+        <v>1.0222</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4555</v>
+        <v>0.5315</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.7723</v>
       </c>
       <c r="K10" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4555</v>
+        <v>2.3038</v>
       </c>
       <c r="N10" t="n">
-        <v>136</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4487</v>
+        <v>2.721</v>
       </c>
       <c r="C11" t="n">
-        <v>0.588</v>
+        <v>0.6534</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5317</v>
+        <v>0.5904</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4487</v>
+        <v>2.721</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6462</v>
+        <v>2.721</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8025</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6462</v>
+        <v>2.721</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5238</v>
+        <v>2.721</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8025</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L11" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3263</v>
+        <v>2.721</v>
       </c>
       <c r="N11" t="n">
-        <v>290</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3027</v>
+        <v>2.6817</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.6439</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4735</v>
+        <v>0.5726</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3027</v>
+        <v>2.6817</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3027</v>
+        <v>2.6817</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3027</v>
+        <v>2.6817</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3027</v>
+        <v>2.6817</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3027</v>
+        <v>2.6817</v>
       </c>
       <c r="N12" t="n">
         <v>154</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1868</v>
+        <v>2.2732</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5251</v>
+        <v>0.5458</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4273</v>
+        <v>0.3882</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1868</v>
+        <v>2.2732</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2092</v>
+        <v>2.9762</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9776</v>
+        <v>-0.703</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2092</v>
+        <v>4.9999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1696</v>
+        <v>2.5997</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9776</v>
+        <v>-0.703</v>
       </c>
       <c r="K13" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="L13" t="n">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1472</v>
+        <v>1.8967</v>
       </c>
       <c r="N13" t="n">
-        <v>247</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8306</v>
+        <v>2.1541</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4396</v>
+        <v>0.5172</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2854</v>
+        <v>0.3345</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8306</v>
+        <v>2.1541</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8306</v>
+        <v>2.1541</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8306</v>
+        <v>2.1541</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8306</v>
+        <v>2.1541</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8306</v>
+        <v>2.1541</v>
       </c>
       <c r="N14" t="n">
         <v>154</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4483</v>
+        <v>2.0794</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3478</v>
+        <v>0.4993</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1331</v>
+        <v>0.3007</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4483</v>
+        <v>2.0794</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0944</v>
+        <v>2.4274</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6461</v>
+        <v>-0.348</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0944</v>
+        <v>3.0662</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6976</v>
+        <v>1.5943</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6461</v>
+        <v>-0.348</v>
       </c>
       <c r="K15" t="n">
         <v>94</v>
@@ -1127,7 +1127,7 @@
         <v>73</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0515</v>
+        <v>1.2463</v>
       </c>
       <c r="N15" t="n">
         <v>167</v>
@@ -1136,127 +1136,127 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4467</v>
+        <v>1.9772</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3474</v>
+        <v>0.4748</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1325</v>
+        <v>0.2546</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4467</v>
+        <v>1.9772</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4467</v>
+        <v>1.2788</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.6984</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4467</v>
+        <v>1.2788</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4467</v>
+        <v>0.6649</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.6984</v>
       </c>
       <c r="K16" t="n">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4467</v>
+        <v>1.3633</v>
       </c>
       <c r="N16" t="n">
-        <v>154</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lukki</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0664</v>
+        <v>1.781</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2561</v>
+        <v>0.4277</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0191</v>
+        <v>0.166</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0664</v>
+        <v>1.781</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0664</v>
+        <v>1.781</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0664</v>
+        <v>1.781</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0664</v>
+        <v>1.781</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0664</v>
+        <v>1.781</v>
       </c>
       <c r="N17" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9232</v>
+        <v>1.6033</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2217</v>
+        <v>0.385</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0761</v>
+        <v>0.0858</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9232</v>
+        <v>1.6033</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9232</v>
+        <v>1.7904</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>-0.1871</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9232</v>
+        <v>1.7904</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5588</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>-0.1871</v>
       </c>
       <c r="K18" t="n">
         <v>48</v>
@@ -1265,7 +1265,7 @@
         <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5588</v>
+        <v>0.7438</v>
       </c>
       <c r="N18" t="n">
         <v>119</v>
@@ -1274,173 +1274,173 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.885</v>
+        <v>1.4374</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2125</v>
+        <v>0.3451</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.0109</v>
       </c>
       <c r="E19" t="n">
-        <v>0.885</v>
+        <v>1.4374</v>
       </c>
       <c r="F19" t="n">
-        <v>0.74</v>
+        <v>2.4374</v>
       </c>
       <c r="G19" t="n">
-        <v>0.145</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.74</v>
+        <v>3.1016</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5998</v>
+        <v>1.6127</v>
       </c>
       <c r="J19" t="n">
-        <v>0.145</v>
+        <v>-1</v>
       </c>
       <c r="K19" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="L19" t="n">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7448</v>
+        <v>0.6127</v>
       </c>
       <c r="N19" t="n">
-        <v>247</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>Lukki</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8757</v>
+        <v>1.1813</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2103</v>
+        <v>0.2837</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.095</v>
+        <v>-0.1047</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8757</v>
+        <v>1.1813</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8757</v>
+        <v>1.1813</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8757</v>
+        <v>1.1813</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8757</v>
+        <v>1.1813</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8757</v>
+        <v>1.1813</v>
       </c>
       <c r="N20" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6639</v>
+        <v>1.1134</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1594</v>
+        <v>0.2673</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1794</v>
+        <v>-0.1354</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6639</v>
+        <v>1.1134</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6639</v>
+        <v>1.1134</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6639</v>
+        <v>1.1134</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6639</v>
+        <v>1.1134</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6639</v>
+        <v>1.1134</v>
       </c>
       <c r="N21" t="n">
-        <v>83</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5454</v>
+        <v>1.1043</v>
       </c>
       <c r="C22" t="n">
-        <v>0.131</v>
+        <v>0.2652</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2266</v>
+        <v>-0.1395</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5454</v>
+        <v>1.1043</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0472</v>
+        <v>1.4047</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5018</v>
+        <v>-0.3004</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0472</v>
+        <v>1.4047</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8488</v>
+        <v>0.7304</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5018</v>
+        <v>-0.3004</v>
       </c>
       <c r="K22" t="n">
         <v>48</v>
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="M22" t="n">
-        <v>0.347</v>
+        <v>0.43</v>
       </c>
       <c r="N22" t="n">
         <v>119</v>
@@ -1458,185 +1458,185 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4068</v>
+        <v>0.9921</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0977</v>
+        <v>0.2382</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2818</v>
+        <v>-0.1901</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4068</v>
+        <v>0.9921</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1479</v>
+        <v>0.9921</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2589</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1479</v>
+        <v>0.9921</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1199</v>
+        <v>0.9921</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2589</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="L23" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3788</v>
+        <v>0.9921</v>
       </c>
       <c r="N23" t="n">
-        <v>119</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3831</v>
+        <v>0.663</v>
       </c>
       <c r="C24" t="n">
-        <v>0.092</v>
+        <v>0.1592</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2913</v>
+        <v>-0.3387</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3831</v>
+        <v>0.663</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3831</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1343</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3831</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3831</v>
+        <v>0.2749</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1343</v>
       </c>
       <c r="K24" t="n">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3831</v>
+        <v>0.4092</v>
       </c>
       <c r="N24" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3672</v>
+        <v>0.6602</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0882</v>
+        <v>0.1585</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2976</v>
+        <v>-0.34</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3672</v>
+        <v>0.6602</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3672</v>
+        <v>0.6602</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3672</v>
+        <v>0.6602</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3672</v>
+        <v>0.6602</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3672</v>
+        <v>0.6602</v>
       </c>
       <c r="N25" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2242</v>
+        <v>0.6463</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0538</v>
+        <v>0.1552</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3546</v>
+        <v>-0.3462</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2242</v>
+        <v>0.6463</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7008</v>
+        <v>0.6463</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4766</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7008</v>
+        <v>0.6463</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6463</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4766</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="L26" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09139999999999993</v>
+        <v>0.6463</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1169</v>
+        <v>0.1445</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0281</v>
+        <v>0.0347</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4905</v>
+        <v>-0.5728</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1169</v>
+        <v>0.1445</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1169</v>
+        <v>0.1445</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1169</v>
+        <v>0.1445</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1169</v>
+        <v>0.1445</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1169</v>
+        <v>0.1445</v>
       </c>
       <c r="N27" t="n">
         <v>83</v>
@@ -1688,124 +1688,124 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Ryxxo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3533</v>
+        <v>-0.0716</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0848</v>
+        <v>-0.0172</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5847</v>
+        <v>-0.6703</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3533</v>
+        <v>-0.0716</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3533</v>
+        <v>-0.0716</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3533</v>
+        <v>-0.0716</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3533</v>
+        <v>-0.0716</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3533</v>
+        <v>-0.0716</v>
       </c>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ryxxo</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4101</v>
+        <v>-0.0893</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0985</v>
+        <v>-0.0214</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6073</v>
+        <v>-0.6783</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4101</v>
+        <v>-0.0893</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4101</v>
+        <v>-0.0893</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4101</v>
+        <v>-0.0893</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4101</v>
+        <v>-0.0893</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4101</v>
+        <v>-0.0893</v>
       </c>
       <c r="N29" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4542</v>
+        <v>-0.1208</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1091</v>
+        <v>-0.029</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6249</v>
+        <v>-0.6925</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4542</v>
+        <v>-0.1208</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4542</v>
+        <v>-0.1208</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4542</v>
+        <v>-0.1208</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4542</v>
+        <v>-0.1208</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4542</v>
+        <v>-0.1208</v>
       </c>
       <c r="N30" t="n">
         <v>136</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.484</v>
+        <v>-0.2004</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1162</v>
+        <v>-0.0481</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6367</v>
+        <v>-0.7285</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.484</v>
+        <v>-0.2004</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.484</v>
+        <v>-0.2004</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.484</v>
+        <v>-0.2004</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.484</v>
+        <v>-0.2004</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.484</v>
+        <v>-0.2004</v>
       </c>
       <c r="N31" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5675</v>
+        <v>-0.247</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1363</v>
+        <v>-0.0593</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.67</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5675</v>
+        <v>-0.247</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5675</v>
+        <v>-0.247</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5675</v>
+        <v>-0.247</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5675</v>
+        <v>-0.247</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5675</v>
+        <v>-0.247</v>
       </c>
       <c r="N32" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6282</v>
+        <v>-0.3044</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1508</v>
+        <v>-0.0731</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6942</v>
+        <v>-0.7754</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6282</v>
+        <v>-0.3044</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6282</v>
+        <v>-0.3044</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6282</v>
+        <v>-0.3044</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6282</v>
+        <v>-0.3044</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6282</v>
+        <v>-0.3044</v>
       </c>
       <c r="N33" t="n">
         <v>84</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6288</v>
+        <v>-0.3827</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.151</v>
+        <v>-0.0919</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6944</v>
+        <v>-0.8108</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6288</v>
+        <v>-0.3827</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6288</v>
+        <v>-0.3827</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6288</v>
+        <v>-0.3827</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6288</v>
+        <v>-0.3827</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6288</v>
+        <v>-0.3827</v>
       </c>
       <c r="N34" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9114</v>
+        <v>-0.5855</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2188</v>
+        <v>-0.1406</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.9023</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9114</v>
+        <v>-0.5855</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4237</v>
+        <v>-0.4181</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4877</v>
+        <v>-0.1674</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4237</v>
+        <v>-0.4181</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3434</v>
+        <v>-0.2174</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4877</v>
+        <v>-0.1674</v>
       </c>
       <c r="K35" t="n">
         <v>94</v>
@@ -2047,7 +2047,7 @@
         <v>73</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.3848</v>
       </c>
       <c r="N35" t="n">
         <v>167</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9786</v>
+        <v>-0.6564</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.235</v>
+        <v>-0.1576</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8338</v>
+        <v>-0.9343</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9786</v>
+        <v>-0.6564</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3387</v>
+        <v>-0.2983</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6399</v>
+        <v>-0.3581</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3387</v>
+        <v>-0.2983</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2745</v>
+        <v>-0.1551</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6399</v>
+        <v>-0.3581</v>
       </c>
       <c r="K36" t="n">
         <v>94</v>
@@ -2093,7 +2093,7 @@
         <v>73</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9144000000000001</v>
+        <v>-0.5132</v>
       </c>
       <c r="N36" t="n">
         <v>167</v>
@@ -2102,231 +2102,231 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9958</v>
+        <v>-0.8313</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2391</v>
+        <v>-0.1996</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8406</v>
+        <v>-1.0133</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9958</v>
+        <v>-0.8313</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0329</v>
+        <v>-0.8313</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0371</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0329</v>
+        <v>-0.8313</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8313</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0371</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="L37" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8001</v>
+        <v>-0.8313</v>
       </c>
       <c r="N37" t="n">
-        <v>290</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1497</v>
+        <v>-0.842</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2761</v>
+        <v>-0.2022</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.902</v>
+        <v>-1.0181</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1497</v>
+        <v>-0.842</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5058</v>
+        <v>-0.842</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5058</v>
+        <v>-0.842</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.41</v>
+        <v>-0.842</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="L38" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0539</v>
+        <v>-0.842</v>
       </c>
       <c r="N38" t="n">
-        <v>167</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2885</v>
+        <v>-0.9559</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3094</v>
+        <v>-0.2295</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-1.0696</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2885</v>
+        <v>-0.9559</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2885</v>
+        <v>-0.5352</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.4207</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2885</v>
+        <v>-0.5352</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2885</v>
+        <v>-0.2783</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.4207</v>
       </c>
       <c r="K39" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2885</v>
+        <v>-0.6990000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>84</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3015</v>
+        <v>-1.161</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3125</v>
+        <v>-0.2788</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9624</v>
+        <v>-1.1621</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3015</v>
+        <v>-1.161</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3015</v>
+        <v>-1.161</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3015</v>
+        <v>-1.161</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3015</v>
+        <v>-1.161</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3015</v>
+        <v>-1.161</v>
       </c>
       <c r="N40" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5879</v>
+        <v>-1.2144</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3813</v>
+        <v>-0.2916</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0765</v>
+        <v>-1.1863</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5879</v>
+        <v>-1.2144</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5879</v>
+        <v>-1.4676</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.2532</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5879</v>
+        <v>-1.4676</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5879</v>
+        <v>-0.7631</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.2532</v>
       </c>
       <c r="K41" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5879</v>
+        <v>-0.5099</v>
       </c>
       <c r="N41" t="n">
-        <v>136</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2545</v>
+        <v>1.1699</v>
       </c>
       <c r="J2" t="n">
-        <v>30.108</v>
+        <v>28.0776</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1337</v>
+        <v>1.0953</v>
       </c>
       <c r="J3" t="n">
-        <v>27.2088</v>
+        <v>26.2872</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5573</v>
+        <v>0.638</v>
       </c>
       <c r="J4" t="n">
-        <v>13.3752</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4571</v>
+        <v>0.542</v>
       </c>
       <c r="J5" t="n">
-        <v>10.9704</v>
+        <v>13.008</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.03</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0192</v>
+        <v>0.0608</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4608</v>
+        <v>1.4592</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2752</v>
+        <v>0.2866</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6048</v>
+        <v>6.8784</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02</v>
+        <v>-0.037</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.48</v>
+        <v>-0.888</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2254</v>
+        <v>-0.1535</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.4096</v>
+        <v>-3.684</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.378</v>
+        <v>-0.2436</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.071999999999999</v>
+        <v>-5.8464</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5471</v>
+        <v>-0.3589</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.1304</v>
+        <v>-8.6136</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.87</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1145</v>
+        <v>-0.117</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.29</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3075</v>
+        <v>-0.2467</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.15</v>
+        <v>-4.934</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.64</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5057</v>
+        <v>-0.3486</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.114</v>
+        <v>-6.972</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5216</v>
+        <v>-0.3578</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.432</v>
+        <v>-7.156</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7058</v>
+        <v>-0.4791</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.116</v>
+        <v>-9.582000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7739</v>
+        <v>0.7053</v>
       </c>
       <c r="J17" t="n">
-        <v>15.478</v>
+        <v>14.106</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.56</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7179</v>
+        <v>0.6542</v>
       </c>
       <c r="J18" t="n">
-        <v>14.358</v>
+        <v>13.084</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.415</v>
+        <v>0.4143</v>
       </c>
       <c r="J19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.286</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3353</v>
+        <v>0.3463</v>
       </c>
       <c r="J20" t="n">
-        <v>6.706</v>
+        <v>6.926</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2406</v>
+        <v>0.2622</v>
       </c>
       <c r="J21" t="n">
-        <v>4.812</v>
+        <v>5.244</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2911</v>
+        <v>1.19</v>
       </c>
       <c r="J22" t="n">
-        <v>30.9864</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.849</v>
+        <v>0.8679</v>
       </c>
       <c r="J23" t="n">
-        <v>20.376</v>
+        <v>20.8296</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.25</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6085</v>
+        <v>0.6674</v>
       </c>
       <c r="J24" t="n">
-        <v>14.604</v>
+        <v>16.0176</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5016</v>
+        <v>0.5737</v>
       </c>
       <c r="J25" t="n">
-        <v>12.0384</v>
+        <v>13.7688</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.96</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.315</v>
+        <v>-0.2322</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.56</v>
+        <v>-5.5728</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2943</v>
+        <v>0.3079</v>
       </c>
       <c r="J27" t="n">
-        <v>7.0632</v>
+        <v>7.3896</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1856</v>
+        <v>0.1687</v>
       </c>
       <c r="J28" t="n">
-        <v>4.4544</v>
+        <v>4.0488</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3587</v>
+        <v>-0.2376</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.6088</v>
+        <v>-5.7024</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.68</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5073</v>
+        <v>-0.3335</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.1752</v>
+        <v>-8.004</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6906</v>
+        <v>-0.4643</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.5744</v>
+        <v>-11.1432</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7024</v>
+        <v>0.5033</v>
       </c>
       <c r="J32" t="n">
-        <v>20.3696</v>
+        <v>14.5957</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5077</v>
+        <v>0.3966</v>
       </c>
       <c r="J33" t="n">
-        <v>14.7233</v>
+        <v>11.5014</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3256</v>
+        <v>0.2852</v>
       </c>
       <c r="J34" t="n">
-        <v>9.442399999999999</v>
+        <v>8.270799999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2665</v>
+        <v>-0.1513</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.7285</v>
+        <v>-4.3877</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2979</v>
+        <v>-0.1733</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.639099999999999</v>
+        <v>-5.0257</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2061</v>
+        <v>0.1571</v>
       </c>
       <c r="J37" t="n">
-        <v>5.9769</v>
+        <v>4.5559</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.01</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0794</v>
+        <v>0.0416</v>
       </c>
       <c r="J38" t="n">
-        <v>2.3026</v>
+        <v>1.2064</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2499</v>
+        <v>-0.1578</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.2471</v>
+        <v>-4.5762</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.743</v>
+        <v>-4.8778</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3772</v>
+        <v>-0.2393</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.9388</v>
+        <v>-6.9397</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5323</v>
+        <v>0.5083</v>
       </c>
       <c r="J42" t="n">
-        <v>13.3075</v>
+        <v>12.7075</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.92</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1296</v>
+        <v>-0.1018</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.24</v>
+        <v>-2.545</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.91</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1495</v>
+        <v>-0.113</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.7375</v>
+        <v>-2.825</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.353</v>
+        <v>-0.2259</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.824999999999999</v>
+        <v>-5.6475</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6899</v>
+        <v>-0.463</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.2475</v>
+        <v>-11.575</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.48</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1631</v>
+        <v>0.8335</v>
       </c>
       <c r="J47" t="n">
-        <v>29.0775</v>
+        <v>20.8375</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.41</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0173</v>
+        <v>0.7436</v>
       </c>
       <c r="J48" t="n">
-        <v>25.4325</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4635</v>
+        <v>0.4494</v>
       </c>
       <c r="J49" t="n">
-        <v>11.5875</v>
+        <v>11.235</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3834</v>
+        <v>0.4051</v>
       </c>
       <c r="J50" t="n">
-        <v>9.585000000000001</v>
+        <v>10.1275</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3405</v>
+        <v>-0.2599</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.512499999999999</v>
+        <v>-6.4975</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.63</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3139</v>
+        <v>-0.2672</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.3363</v>
+        <v>-4.5424</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.39</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.7296</v>
+        <v>-0.5252</v>
       </c>
       <c r="J53" t="n">
-        <v>-12.4032</v>
+        <v>-8.9284</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.37</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.5441</v>
       </c>
       <c r="J54" t="n">
-        <v>-13.0492</v>
+        <v>-9.249700000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.33</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8348</v>
+        <v>-0.584</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.1916</v>
+        <v>-9.928000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.3</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8815</v>
+        <v>-0.615</v>
       </c>
       <c r="J56" t="n">
-        <v>-14.9855</v>
+        <v>-10.455</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.27</v>
       </c>
       <c r="I57" t="n">
-        <v>2.0666</v>
+        <v>1.6361</v>
       </c>
       <c r="J57" t="n">
-        <v>35.1322</v>
+        <v>27.8137</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.77</v>
       </c>
       <c r="I58" t="n">
-        <v>1.5099</v>
+        <v>1.1042</v>
       </c>
       <c r="J58" t="n">
-        <v>25.6683</v>
+        <v>18.7714</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.66</v>
       </c>
       <c r="I59" t="n">
-        <v>1.2722</v>
+        <v>0.9858</v>
       </c>
       <c r="J59" t="n">
-        <v>21.6274</v>
+        <v>16.7586</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.47</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.7649</v>
       </c>
       <c r="J60" t="n">
-        <v>15.3119</v>
+        <v>13.0033</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6816</v>
+        <v>0.627</v>
       </c>
       <c r="J61" t="n">
-        <v>11.5872</v>
+        <v>10.659</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.77</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0009</v>
+        <v>0.6783</v>
       </c>
       <c r="J62" t="n">
-        <v>25.0225</v>
+        <v>16.9575</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.21</v>
+        <v>0.2092</v>
       </c>
       <c r="J63" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.09</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1259</v>
+        <v>0.1406</v>
       </c>
       <c r="J64" t="n">
-        <v>3.1475</v>
+        <v>3.515</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1841</v>
+        <v>-0.094</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.6025</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2198</v>
+        <v>-0.1185</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.495</v>
+        <v>-2.9625</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.349</v>
+        <v>0.2959</v>
       </c>
       <c r="J67" t="n">
-        <v>8.725</v>
+        <v>7.3975</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0391</v>
+        <v>0.0094</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9775</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1129</v>
+        <v>-0.0824</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.8225</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3508</v>
+        <v>-0.2208</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.77</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4382</v>
+        <v>-0.2801</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.955</v>
+        <v>-7.0025</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5458</v>
+        <v>0.5216</v>
       </c>
       <c r="J72" t="n">
-        <v>12.5534</v>
+        <v>11.9968</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.4369</v>
+        <v>-0.2904</v>
       </c>
       <c r="J73" t="n">
-        <v>-10.0487</v>
+        <v>-6.6792</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.72</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4369</v>
+        <v>-0.2904</v>
       </c>
       <c r="J74" t="n">
-        <v>-10.0487</v>
+        <v>-6.6792</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4814</v>
+        <v>-0.3189</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.0722</v>
+        <v>-7.3347</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6448</v>
+        <v>-0.4315</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.8304</v>
+        <v>-9.9245</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2749</v>
+        <v>0.9025</v>
       </c>
       <c r="J77" t="n">
-        <v>29.3227</v>
+        <v>20.7575</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0928</v>
+        <v>0.7873</v>
       </c>
       <c r="J78" t="n">
-        <v>25.1344</v>
+        <v>18.1079</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1709</v>
+        <v>0.2415</v>
       </c>
       <c r="J79" t="n">
-        <v>3.9307</v>
+        <v>5.5545</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1407</v>
+        <v>0.2115</v>
       </c>
       <c r="J80" t="n">
-        <v>3.2361</v>
+        <v>4.8645</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.95</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.333</v>
+        <v>-0.254</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.659</v>
+        <v>-5.842</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.15</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3412</v>
+        <v>0.3581</v>
       </c>
       <c r="J82" t="n">
-        <v>8.529999999999999</v>
+        <v>8.952500000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0128</v>
+        <v>-0.0118</v>
       </c>
       <c r="J83" t="n">
-        <v>0.32</v>
+        <v>-0.295</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3289</v>
+        <v>-0.2083</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.2225</v>
+        <v>-5.2075</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3444</v>
+        <v>-0.2184</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.609999999999999</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3747</v>
+        <v>-0.2383</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.3675</v>
+        <v>-5.9575</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.38</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9534</v>
+        <v>0.705</v>
       </c>
       <c r="J87" t="n">
-        <v>23.835</v>
+        <v>17.625</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.841</v>
+        <v>0.6392</v>
       </c>
       <c r="J88" t="n">
-        <v>21.025</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.32</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8177</v>
+        <v>0.6259</v>
       </c>
       <c r="J89" t="n">
-        <v>20.4425</v>
+        <v>15.6475</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.18</v>
       </c>
       <c r="I90" t="n">
-        <v>0.438</v>
+        <v>0.4351</v>
       </c>
       <c r="J90" t="n">
-        <v>10.95</v>
+        <v>10.8775</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2728</v>
+        <v>-0.191</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.82</v>
+        <v>-4.775</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.35</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9408</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>26.3424</v>
+        <v>26.0092</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7817</v>
+        <v>0.7664</v>
       </c>
       <c r="J93" t="n">
-        <v>21.8876</v>
+        <v>21.4592</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5834</v>
+        <v>0.5728</v>
       </c>
       <c r="J94" t="n">
-        <v>16.3352</v>
+        <v>16.0384</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0794</v>
+        <v>0.1351</v>
       </c>
       <c r="J95" t="n">
-        <v>2.2232</v>
+        <v>3.7828</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6333</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.292</v>
+        <v>-17.7324</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2054</v>
+        <v>0.213</v>
       </c>
       <c r="J97" t="n">
-        <v>5.7512</v>
+        <v>5.964</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1491</v>
+        <v>0.1464</v>
       </c>
       <c r="J98" t="n">
-        <v>4.1748</v>
+        <v>4.0992</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1072</v>
+        <v>0.0982</v>
       </c>
       <c r="J99" t="n">
-        <v>3.0016</v>
+        <v>2.7496</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2512</v>
+        <v>-0.1525</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.0336</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3758</v>
+        <v>-0.2352</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.5224</v>
+        <v>-6.5856</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.12</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5251</v>
+        <v>0.4561</v>
       </c>
       <c r="J102" t="n">
-        <v>18.9036</v>
+        <v>16.4196</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.098</v>
+        <v>0.0327</v>
       </c>
       <c r="J103" t="n">
-        <v>3.528</v>
+        <v>1.1772</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.84</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5026</v>
+        <v>-0.4824</v>
       </c>
       <c r="J104" t="n">
-        <v>-18.0936</v>
+        <v>-17.3664</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5595</v>
+        <v>-0.535</v>
       </c>
       <c r="J105" t="n">
-        <v>-20.142</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.68</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9122</v>
+        <v>-0.8891</v>
       </c>
       <c r="J106" t="n">
-        <v>-32.8392</v>
+        <v>-32.0076</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.7</v>
       </c>
       <c r="I107" t="n">
-        <v>0.921</v>
+        <v>1.1039</v>
       </c>
       <c r="J107" t="n">
-        <v>33.156</v>
+        <v>39.7404</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3539</v>
+        <v>0.4451</v>
       </c>
       <c r="J108" t="n">
-        <v>12.7404</v>
+        <v>16.0236</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2325</v>
+        <v>0.3265</v>
       </c>
       <c r="J109" t="n">
-        <v>8.369999999999999</v>
+        <v>11.754</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1049</v>
+        <v>-0.04</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.7764</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2247</v>
+        <v>-0.121</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.0892</v>
+        <v>-4.356</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.32</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9069</v>
+        <v>0.8848</v>
       </c>
       <c r="J112" t="n">
-        <v>27.207</v>
+        <v>26.544</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.24</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7208</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>21.624</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.1</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3401</v>
+        <v>0.3271</v>
       </c>
       <c r="J114" t="n">
-        <v>10.203</v>
+        <v>9.813000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2706</v>
+        <v>0.271</v>
       </c>
       <c r="J115" t="n">
-        <v>8.118</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.0572</v>
+        <v>-1.0398</v>
       </c>
       <c r="J116" t="n">
-        <v>-31.716</v>
+        <v>-31.194</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5312</v>
+        <v>0.6322</v>
       </c>
       <c r="J117" t="n">
-        <v>15.936</v>
+        <v>18.966</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.19</v>
       </c>
       <c r="I118" t="n">
-        <v>0.367</v>
+        <v>0.4184</v>
       </c>
       <c r="J118" t="n">
-        <v>11.01</v>
+        <v>12.552</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.03</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0891</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>2.673</v>
+        <v>2.724</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.77</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4274</v>
+        <v>-0.2695</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.822</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.73</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4818</v>
+        <v>-0.3083</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.454</v>
+        <v>-9.249000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.52</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1995</v>
+        <v>1.1393</v>
       </c>
       <c r="J122" t="n">
-        <v>29.9875</v>
+        <v>28.4825</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.47</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0972</v>
+        <v>1.0775</v>
       </c>
       <c r="J123" t="n">
-        <v>27.43</v>
+        <v>26.9375</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.42</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.0094</v>
       </c>
       <c r="J124" t="n">
-        <v>24.76</v>
+        <v>25.235</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.26</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5893</v>
+        <v>0.6783</v>
       </c>
       <c r="J125" t="n">
-        <v>14.7325</v>
+        <v>16.9575</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.98</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2628</v>
+        <v>-0.1757</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.57</v>
+        <v>-4.3925</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4607</v>
+        <v>0.5324</v>
       </c>
       <c r="J127" t="n">
-        <v>11.5175</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.82</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2588</v>
+        <v>-0.196</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.47</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.78</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.341</v>
+        <v>-0.2339</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.525</v>
+        <v>-5.8475</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5934</v>
+        <v>-0.3948</v>
       </c>
       <c r="J130" t="n">
-        <v>-14.835</v>
+        <v>-9.869999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.4321</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.1425</v>
+        <v>-10.8025</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.47</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1358</v>
+        <v>1.0916</v>
       </c>
       <c r="J132" t="n">
-        <v>31.8024</v>
+        <v>30.5648</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8777</v>
+        <v>0.8925</v>
       </c>
       <c r="J133" t="n">
-        <v>24.5756</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6549</v>
+        <v>0.6908</v>
       </c>
       <c r="J134" t="n">
-        <v>18.3372</v>
+        <v>19.3424</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.15</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3497</v>
+        <v>0.4258</v>
       </c>
       <c r="J135" t="n">
-        <v>9.791600000000001</v>
+        <v>11.9224</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0043</v>
+        <v>0.0717</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.1204</v>
+        <v>2.0076</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4234</v>
+        <v>0.4836</v>
       </c>
       <c r="J137" t="n">
-        <v>11.8552</v>
+        <v>13.5408</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1845</v>
+        <v>0.1803</v>
       </c>
       <c r="J138" t="n">
-        <v>5.166</v>
+        <v>5.0484</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2359</v>
+        <v>-0.1481</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.6052</v>
+        <v>-4.1468</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3647</v>
+        <v>-0.2304</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.2116</v>
+        <v>-6.4512</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5191</v>
+        <v>-0.3372</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.5348</v>
+        <v>-9.441599999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.29</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7497</v>
+        <v>0.763</v>
       </c>
       <c r="J142" t="n">
-        <v>20.2419</v>
+        <v>20.601</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7251</v>
+        <v>0.7402</v>
       </c>
       <c r="J143" t="n">
-        <v>19.5777</v>
+        <v>19.9854</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.24</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6192</v>
+        <v>0.6486</v>
       </c>
       <c r="J144" t="n">
-        <v>16.7184</v>
+        <v>17.5122</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.19</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4687</v>
+        <v>0.5314</v>
       </c>
       <c r="J145" t="n">
-        <v>12.6549</v>
+        <v>14.3478</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I146" t="n">
-        <v>0.3607</v>
+        <v>0.4307</v>
       </c>
       <c r="J146" t="n">
-        <v>9.738899999999999</v>
+        <v>11.6289</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.7758</v>
       </c>
       <c r="J147" t="n">
-        <v>17.1882</v>
+        <v>20.9466</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.9</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1672</v>
+        <v>-0.1235</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.5144</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.85</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.27</v>
+        <v>-0.175</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.29</v>
+        <v>-4.725</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5233</v>
+        <v>-0.3416</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.1291</v>
+        <v>-9.2232</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.3699</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.201</v>
+        <v>-9.987299999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.15</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3517</v>
+        <v>0.3863</v>
       </c>
       <c r="J152" t="n">
-        <v>10.551</v>
+        <v>11.589</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2552</v>
+        <v>0.2619</v>
       </c>
       <c r="J153" t="n">
-        <v>7.656</v>
+        <v>7.857</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1447</v>
+        <v>-0.1122</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.341</v>
+        <v>-3.366</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.73</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4535</v>
+        <v>-0.2933</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.605</v>
+        <v>-8.798999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7007</v>
+        <v>-0.4712</v>
       </c>
       <c r="J156" t="n">
-        <v>-21.021</v>
+        <v>-14.136</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.22</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6301</v>
+        <v>0.6197</v>
       </c>
       <c r="J157" t="n">
-        <v>18.903</v>
+        <v>18.591</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>18.129</v>
+        <v>17.859</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.19</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5511</v>
+        <v>0.5461</v>
       </c>
       <c r="J159" t="n">
-        <v>16.533</v>
+        <v>16.383</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4654</v>
+        <v>0.4715</v>
       </c>
       <c r="J160" t="n">
-        <v>13.962</v>
+        <v>14.145</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3405</v>
+        <v>-0.2682</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.215</v>
+        <v>-8.045999999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.25</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4543</v>
+        <v>0.5298</v>
       </c>
       <c r="J162" t="n">
-        <v>13.1747</v>
+        <v>15.3642</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4128</v>
+        <v>0.4759</v>
       </c>
       <c r="J163" t="n">
-        <v>11.9712</v>
+        <v>13.8011</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0391</v>
+        <v>-0.0204</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.1339</v>
+        <v>-0.5916</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3975</v>
+        <v>-0.2488</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.5275</v>
+        <v>-7.2152</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4668</v>
+        <v>-0.2977</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.5372</v>
+        <v>-8.6333</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3025</v>
+        <v>1.1894</v>
       </c>
       <c r="J167" t="n">
-        <v>37.7725</v>
+        <v>34.4926</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6197</v>
+        <v>0.602</v>
       </c>
       <c r="J168" t="n">
-        <v>17.9713</v>
+        <v>17.458</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1565</v>
+        <v>0.2035</v>
       </c>
       <c r="J169" t="n">
-        <v>4.5385</v>
+        <v>5.9015</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.01</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0302</v>
+        <v>0.0267</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.8758</v>
+        <v>0.7743</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7086</v>
+        <v>-0.6551</v>
       </c>
       <c r="J171" t="n">
-        <v>-20.5494</v>
+        <v>-18.9979</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2258</v>
+        <v>1.1388</v>
       </c>
       <c r="J172" t="n">
-        <v>72.3222</v>
+        <v>67.1892</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2589</v>
+        <v>0.2933</v>
       </c>
       <c r="J173" t="n">
-        <v>15.2751</v>
+        <v>17.3047</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.02</v>
       </c>
       <c r="I174" t="n">
-        <v>0.016</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>0.944</v>
+        <v>4.0769</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0868</v>
+        <v>-0.0265</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.1212</v>
+        <v>-1.5635</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1891</v>
+        <v>-0.1224</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.1569</v>
+        <v>-7.2216</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.27</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4732</v>
+        <v>0.5568</v>
       </c>
       <c r="J177" t="n">
-        <v>27.9188</v>
+        <v>32.8512</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.08</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1836</v>
+        <v>0.2001</v>
       </c>
       <c r="J178" t="n">
-        <v>10.8324</v>
+        <v>11.8059</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0206</v>
+        <v>0.0354</v>
       </c>
       <c r="J179" t="n">
-        <v>1.2154</v>
+        <v>2.0886</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0524</v>
+        <v>-0.0223</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.0916</v>
+        <v>-1.3157</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4444</v>
+        <v>-0.2811</v>
       </c>
       <c r="J181" t="n">
-        <v>-26.2196</v>
+        <v>-16.5849</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6921</v>
+        <v>0.8563</v>
       </c>
       <c r="J182" t="n">
-        <v>17.9946</v>
+        <v>22.2638</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1469</v>
+        <v>0.1258</v>
       </c>
       <c r="J183" t="n">
-        <v>3.8194</v>
+        <v>3.2708</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.93</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0998</v>
+        <v>-0.0877</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.5948</v>
+        <v>-2.2802</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.7229</v>
+        <v>-0.4881</v>
       </c>
       <c r="J185" t="n">
-        <v>-18.7954</v>
+        <v>-12.6906</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.48</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7706</v>
+        <v>-0.5245</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.0356</v>
+        <v>-13.637</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.67</v>
       </c>
       <c r="I187" t="n">
-        <v>1.5369</v>
+        <v>1.3484</v>
       </c>
       <c r="J187" t="n">
-        <v>39.9594</v>
+        <v>35.0584</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.25</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6523</v>
+        <v>0.6725</v>
       </c>
       <c r="J188" t="n">
-        <v>16.9598</v>
+        <v>17.485</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2814</v>
+        <v>0.3523</v>
       </c>
       <c r="J189" t="n">
-        <v>7.3164</v>
+        <v>9.159800000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.196</v>
+        <v>0.2683</v>
       </c>
       <c r="J190" t="n">
-        <v>5.096</v>
+        <v>6.9758</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.99</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1902</v>
+        <v>-0.1095</v>
       </c>
       <c r="J191" t="n">
-        <v>-4.9452</v>
+        <v>-2.847</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.28</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7719</v>
       </c>
       <c r="J192" t="n">
-        <v>22.1424</v>
+        <v>21.6132</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.26</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="J193" t="n">
-        <v>20.8152</v>
+        <v>20.2692</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6702</v>
+        <v>0.6511</v>
       </c>
       <c r="J194" t="n">
-        <v>18.7656</v>
+        <v>18.2308</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.2</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5939</v>
+        <v>0.5772</v>
       </c>
       <c r="J195" t="n">
-        <v>16.6292</v>
+        <v>16.1616</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.63</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.0878</v>
+        <v>-1.0741</v>
       </c>
       <c r="J196" t="n">
-        <v>-30.4584</v>
+        <v>-30.0748</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.2</v>
       </c>
       <c r="I197" t="n">
-        <v>0.392</v>
+        <v>0.4467</v>
       </c>
       <c r="J197" t="n">
-        <v>10.976</v>
+        <v>12.5076</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.333</v>
+        <v>0.3714</v>
       </c>
       <c r="J198" t="n">
-        <v>9.324</v>
+        <v>10.3992</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1452</v>
+        <v>-0.0857</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.0656</v>
+        <v>-2.3996</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2703</v>
+        <v>-0.1641</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.5684</v>
+        <v>-4.5948</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5026</v>
+        <v>-0.324</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.0728</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.83</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.2172</v>
+        <v>-0.1791</v>
       </c>
       <c r="J202" t="n">
-        <v>-4.7784</v>
+        <v>-3.9402</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.83</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2172</v>
+        <v>-0.1791</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.7784</v>
+        <v>-3.9402</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3192</v>
+        <v>-0.2392</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.0224</v>
+        <v>-5.2624</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3624</v>
+        <v>-0.2575</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.9728</v>
+        <v>-5.665</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6212</v>
+        <v>-0.4162</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.6664</v>
+        <v>-9.1564</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.61</v>
       </c>
       <c r="I207" t="n">
-        <v>1.38</v>
+        <v>1.2513</v>
       </c>
       <c r="J207" t="n">
-        <v>30.36</v>
+        <v>27.5286</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.039</v>
+        <v>1.0404</v>
       </c>
       <c r="J208" t="n">
-        <v>22.858</v>
+        <v>22.8888</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.38</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9065</v>
+        <v>0.9402</v>
       </c>
       <c r="J209" t="n">
-        <v>19.943</v>
+        <v>20.6844</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.372</v>
+        <v>0.4621</v>
       </c>
       <c r="J210" t="n">
-        <v>8.183999999999999</v>
+        <v>10.1662</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1615</v>
+        <v>-0.0774</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.553</v>
+        <v>-1.7028</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.26</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4693</v>
+        <v>0.5491</v>
       </c>
       <c r="J212" t="n">
-        <v>16.4255</v>
+        <v>19.2185</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2302</v>
+        <v>0.2479</v>
       </c>
       <c r="J213" t="n">
-        <v>8.057</v>
+        <v>8.676500000000001</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1721</v>
+        <v>-0.0994</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.0235</v>
+        <v>-3.479</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.226</v>
+        <v>-0.1336</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.91</v>
+        <v>-4.676</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4108</v>
+        <v>-0.2582</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.378</v>
+        <v>-9.037000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.47</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2129</v>
+        <v>1.1298</v>
       </c>
       <c r="J217" t="n">
-        <v>42.4515</v>
+        <v>39.543</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4718</v>
+        <v>0.4555</v>
       </c>
       <c r="J218" t="n">
-        <v>16.513</v>
+        <v>15.9425</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2209</v>
+        <v>-0.1559</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.7315</v>
+        <v>-5.4565</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2566</v>
+        <v>-0.1909</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.981</v>
+        <v>-6.6815</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2905</v>
+        <v>-0.2242</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.1675</v>
+        <v>-7.847</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.37</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9282</v>
+        <v>0.9379</v>
       </c>
       <c r="J222" t="n">
-        <v>23.205</v>
+        <v>23.4475</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7664</v>
+        <v>0.783</v>
       </c>
       <c r="J223" t="n">
-        <v>19.16</v>
+        <v>19.575</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.22</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5419</v>
+        <v>0.6012</v>
       </c>
       <c r="J224" t="n">
-        <v>13.5475</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.18</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4345</v>
+        <v>0.5043</v>
       </c>
       <c r="J225" t="n">
-        <v>10.8625</v>
+        <v>12.6075</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3277</v>
+        <v>0.4018</v>
       </c>
       <c r="J226" t="n">
-        <v>8.192500000000001</v>
+        <v>10.045</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.11</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3019</v>
+        <v>0.3191</v>
       </c>
       <c r="J227" t="n">
-        <v>7.5475</v>
+        <v>7.9775</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.89</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1637</v>
+        <v>-0.1302</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.0925</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3682</v>
+        <v>-0.2403</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.205</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.77</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3837</v>
+        <v>-0.2501</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.592499999999999</v>
+        <v>-6.2525</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4859</v>
+        <v>-0.3175</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.1475</v>
+        <v>-7.9375</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2569/event_2569_evp_summary.xlsx
+++ b/database/event/2569/event_2569_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4274</v>
+        <v>5.3264</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3032</v>
+        <v>1.279</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8122</v>
+        <v>1.8005</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4274</v>
+        <v>5.3264</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0106</v>
+        <v>2.9266</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4168</v>
+        <v>2.3998</v>
       </c>
       <c r="H2" t="n">
-        <v>5.121</v>
+        <v>4.7617</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6627</v>
+        <v>2.5713</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4168</v>
+        <v>2.3998</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>5.079499999999999</v>
+        <v>4.9711</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6109</v>
+        <v>4.6304</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1072</v>
+        <v>1.1118</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4436</v>
+        <v>1.4836</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6109</v>
+        <v>4.6304</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9733</v>
+        <v>1.8228</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6376</v>
+        <v>2.8076</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9733</v>
+        <v>1.8228</v>
       </c>
       <c r="I3" t="n">
-        <v>1.026</v>
+        <v>0.9843</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6376</v>
+        <v>2.8076</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6636</v>
+        <v>3.7919</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5661</v>
+        <v>4.4937</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0964</v>
+        <v>1.079</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4234</v>
+        <v>1.4214</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5661</v>
+        <v>4.4937</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2426</v>
+        <v>3.1334</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3235</v>
+        <v>1.3603</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9386</v>
+        <v>5.4442</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0878</v>
+        <v>2.9398</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3235</v>
+        <v>1.3603</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -621,7 +621,7 @@
         <v>141</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4113</v>
+        <v>4.3001</v>
       </c>
       <c r="N4" t="n">
         <v>247</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0485</v>
+        <v>4.0916</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9721</v>
+        <v>0.9825</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1897</v>
+        <v>1.2384</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0485</v>
+        <v>4.0916</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9669</v>
+        <v>1.573</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0816</v>
+        <v>2.5187</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9669</v>
+        <v>1.573</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0227</v>
+        <v>0.8494</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0816</v>
+        <v>2.5187</v>
       </c>
       <c r="K5" t="n">
         <v>151</v>
@@ -667,7 +667,7 @@
         <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1043</v>
+        <v>3.3681</v>
       </c>
       <c r="N5" t="n">
         <v>290</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9943</v>
+        <v>3.9837</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9591</v>
+        <v>0.9566</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1652</v>
+        <v>1.1893</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9943</v>
+        <v>3.9837</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6688</v>
+        <v>1.7545</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3255</v>
+        <v>2.2292</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6688</v>
+        <v>1.7545</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8677</v>
+        <v>0.9474</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3255</v>
+        <v>2.2292</v>
       </c>
       <c r="K6" t="n">
         <v>151</v>
@@ -713,7 +713,7 @@
         <v>139</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1932</v>
+        <v>3.1766</v>
       </c>
       <c r="N6" t="n">
         <v>290</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3154</v>
+        <v>3.3841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7961</v>
+        <v>0.8126</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8587</v>
+        <v>0.9163</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3154</v>
+        <v>3.3841</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3339</v>
+        <v>1.3354</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9815</v>
+        <v>2.0487</v>
       </c>
       <c r="H7" t="n">
-        <v>2.737</v>
+        <v>1.3354</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4231</v>
+        <v>0.7211</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9815</v>
+        <v>2.0487</v>
       </c>
       <c r="K7" t="n">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="L7" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4046</v>
+        <v>2.7698</v>
       </c>
       <c r="N7" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2721</v>
+        <v>3.3689</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7857</v>
+        <v>0.8089</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.9094</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2721</v>
+        <v>3.3689</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3563</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9158</v>
+        <v>1.1089</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3563</v>
+        <v>2.5623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7052</v>
+        <v>1.3836</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9158</v>
+        <v>1.1089</v>
       </c>
       <c r="K8" t="n">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="L8" t="n">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="M8" t="n">
-        <v>2.621</v>
+        <v>2.4925</v>
       </c>
       <c r="N8" t="n">
-        <v>290</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8461</v>
+        <v>2.8691</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6834</v>
+        <v>0.6889</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6469</v>
+        <v>0.6819</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8461</v>
+        <v>2.8691</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2667</v>
+        <v>1.1246</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5794</v>
+        <v>1.7445</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2667</v>
+        <v>1.1246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6586</v>
+        <v>0.6073</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5794</v>
+        <v>1.7445</v>
       </c>
       <c r="K9" t="n">
         <v>151</v>
@@ -851,7 +851,7 @@
         <v>139</v>
       </c>
       <c r="M9" t="n">
-        <v>2.238</v>
+        <v>2.3518</v>
       </c>
       <c r="N9" t="n">
         <v>290</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7945</v>
+        <v>2.8497</v>
       </c>
       <c r="C10" t="n">
-        <v>0.671</v>
+        <v>0.6843</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6236</v>
+        <v>0.673</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7945</v>
+        <v>2.8497</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0222</v>
+        <v>0.925</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7723</v>
+        <v>1.9247</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0222</v>
+        <v>0.925</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5315</v>
+        <v>0.4995</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7723</v>
+        <v>1.9247</v>
       </c>
       <c r="K10" t="n">
         <v>106</v>
@@ -897,7 +897,7 @@
         <v>141</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3038</v>
+        <v>2.4242</v>
       </c>
       <c r="N10" t="n">
         <v>247</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.721</v>
+        <v>2.4327</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6534</v>
+        <v>0.5841</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5904</v>
+        <v>0.4832</v>
       </c>
       <c r="E11" t="n">
-        <v>2.721</v>
+        <v>2.4327</v>
       </c>
       <c r="F11" t="n">
-        <v>2.721</v>
+        <v>2.4327</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.721</v>
+        <v>2.5994</v>
       </c>
       <c r="I11" t="n">
-        <v>2.721</v>
+        <v>2.5994</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.721</v>
+        <v>2.5994</v>
       </c>
       <c r="N11" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6817</v>
+        <v>2.4314</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6439</v>
+        <v>0.5838</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5726</v>
+        <v>0.4826</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6817</v>
+        <v>2.4314</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6817</v>
+        <v>2.4314</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6817</v>
+        <v>2.5966</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6817</v>
+        <v>2.5966</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6817</v>
+        <v>2.5966</v>
       </c>
       <c r="N12" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2732</v>
+        <v>2.2041</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5458</v>
+        <v>0.5292</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3882</v>
+        <v>0.3791</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2732</v>
+        <v>2.2041</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9762</v>
+        <v>2.9162</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.703</v>
+        <v>-0.7121</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9999</v>
+        <v>4.7273</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5997</v>
+        <v>2.5527</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.703</v>
+        <v>-0.7121</v>
       </c>
       <c r="K13" t="n">
         <v>48</v>
@@ -1035,7 +1035,7 @@
         <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8967</v>
+        <v>1.8406</v>
       </c>
       <c r="N13" t="n">
         <v>119</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1541</v>
+        <v>2.0773</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5172</v>
+        <v>0.4988</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3345</v>
+        <v>0.3214</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1541</v>
+        <v>2.0773</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1541</v>
+        <v>2.0773</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1541</v>
+        <v>2.0773</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1541</v>
+        <v>2.0773</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1541</v>
+        <v>2.0773</v>
       </c>
       <c r="N14" t="n">
         <v>154</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0794</v>
+        <v>1.9864</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4993</v>
+        <v>0.477</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3007</v>
+        <v>0.28</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0794</v>
+        <v>1.9864</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4274</v>
+        <v>2.3494</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.348</v>
+        <v>-0.363</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0662</v>
+        <v>2.8575</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5943</v>
+        <v>1.543</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.348</v>
+        <v>-0.363</v>
       </c>
       <c r="K15" t="n">
         <v>94</v>
@@ -1127,7 +1127,7 @@
         <v>73</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2463</v>
+        <v>1.18</v>
       </c>
       <c r="N15" t="n">
         <v>167</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9772</v>
+        <v>1.8774</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4748</v>
+        <v>0.4508</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2546</v>
+        <v>0.2304</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9772</v>
+        <v>1.8774</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2788</v>
+        <v>1.2104</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6984</v>
+        <v>0.667</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2788</v>
+        <v>1.2104</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6649</v>
+        <v>0.6536</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6984</v>
+        <v>0.667</v>
       </c>
       <c r="K16" t="n">
         <v>106</v>
@@ -1173,7 +1173,7 @@
         <v>141</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3633</v>
+        <v>1.3206</v>
       </c>
       <c r="N16" t="n">
         <v>247</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.781</v>
+        <v>1.7248</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4277</v>
+        <v>0.4142</v>
       </c>
       <c r="D17" t="n">
-        <v>0.166</v>
+        <v>0.161</v>
       </c>
       <c r="E17" t="n">
-        <v>1.781</v>
+        <v>1.7248</v>
       </c>
       <c r="F17" t="n">
-        <v>1.781</v>
+        <v>1.7248</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.781</v>
+        <v>1.7248</v>
       </c>
       <c r="I17" t="n">
-        <v>1.781</v>
+        <v>1.7248</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.781</v>
+        <v>1.7248</v>
       </c>
       <c r="N17" t="n">
         <v>154</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6033</v>
+        <v>1.4991</v>
       </c>
       <c r="C18" t="n">
-        <v>0.385</v>
+        <v>0.36</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0858</v>
+        <v>0.0582</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6033</v>
+        <v>1.4991</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7904</v>
+        <v>1.6608</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1871</v>
+        <v>-0.1617</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7904</v>
+        <v>1.6608</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.8968</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1871</v>
+        <v>-0.1617</v>
       </c>
       <c r="K18" t="n">
         <v>48</v>
@@ -1265,7 +1265,7 @@
         <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7438</v>
+        <v>0.7351000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>119</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4374</v>
+        <v>1.3453</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3451</v>
+        <v>0.323</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0109</v>
+        <v>-0.0118</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4374</v>
+        <v>1.3453</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4374</v>
+        <v>2.3453</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1016</v>
+        <v>2.8439</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6127</v>
+        <v>1.5357</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>71</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6127</v>
+        <v>0.5357000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>119</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1813</v>
+        <v>1.1548</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2837</v>
+        <v>0.2773</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1047</v>
+        <v>-0.0985</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1813</v>
+        <v>1.1548</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1813</v>
+        <v>1.1548</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1813</v>
+        <v>1.1548</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1813</v>
+        <v>1.1548</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1813</v>
+        <v>1.1548</v>
       </c>
       <c r="N20" t="n">
         <v>84</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1134</v>
+        <v>1.0963</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673</v>
+        <v>0.2632</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1354</v>
+        <v>-0.1251</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1134</v>
+        <v>1.0963</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1134</v>
+        <v>1.3737</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.2774</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1134</v>
+        <v>1.3737</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1134</v>
+        <v>0.7418</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.2774</v>
       </c>
       <c r="K21" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1134</v>
+        <v>0.4644</v>
       </c>
       <c r="N21" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1043</v>
+        <v>1.0712</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2652</v>
+        <v>0.2572</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1395</v>
+        <v>-0.1366</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1043</v>
+        <v>1.0712</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4047</v>
+        <v>1.0712</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3004</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4047</v>
+        <v>1.0712</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7304</v>
+        <v>1.0712</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3004</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="L22" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.43</v>
+        <v>1.0712</v>
       </c>
       <c r="N22" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9921</v>
+        <v>0.9256</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2382</v>
+        <v>0.2223</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1901</v>
+        <v>-0.2029</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9921</v>
+        <v>0.9256</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9921</v>
+        <v>0.9256</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9921</v>
+        <v>0.9256</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9921</v>
+        <v>0.9256</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9921</v>
+        <v>0.9256</v>
       </c>
       <c r="N23" t="n">
         <v>83</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.663</v>
+        <v>0.7146</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1592</v>
+        <v>0.1716</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3387</v>
+        <v>-0.2989</v>
       </c>
       <c r="E24" t="n">
-        <v>0.663</v>
+        <v>0.7146</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5624</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1343</v>
+        <v>0.1522</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5624</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2749</v>
+        <v>0.3037</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1343</v>
+        <v>0.1522</v>
       </c>
       <c r="K24" t="n">
         <v>48</v>
@@ -1541,7 +1541,7 @@
         <v>71</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4092</v>
+        <v>0.4559</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6602</v>
+        <v>0.6352</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1585</v>
+        <v>0.1525</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.34</v>
+        <v>-0.335</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6602</v>
+        <v>0.6352</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6602</v>
+        <v>0.6352</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6602</v>
+        <v>0.6352</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6602</v>
+        <v>0.6352</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6602</v>
+        <v>0.6352</v>
       </c>
       <c r="N25" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6463</v>
+        <v>0.5889</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1552</v>
+        <v>0.1414</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3462</v>
+        <v>-0.3561</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6463</v>
+        <v>0.5889</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6463</v>
+        <v>0.5889</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6463</v>
+        <v>0.5889</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6463</v>
+        <v>0.5889</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6463</v>
+        <v>0.5889</v>
       </c>
       <c r="N26" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1445</v>
+        <v>0.1006</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0347</v>
+        <v>0.0242</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5728</v>
+        <v>-0.5784</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1445</v>
+        <v>0.1006</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1445</v>
+        <v>0.1006</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1445</v>
+        <v>0.1006</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1445</v>
+        <v>0.1006</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1445</v>
+        <v>0.1006</v>
       </c>
       <c r="N27" t="n">
         <v>83</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0716</v>
+        <v>-0.1084</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0172</v>
+        <v>-0.026</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6703</v>
+        <v>-0.6735</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0716</v>
+        <v>-0.1084</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0716</v>
+        <v>-0.1084</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0716</v>
+        <v>-0.1084</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0716</v>
+        <v>-0.1084</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0716</v>
+        <v>-0.1084</v>
       </c>
       <c r="N28" t="n">
         <v>84</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0893</v>
+        <v>-0.1194</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0214</v>
+        <v>-0.0287</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6783</v>
+        <v>-0.6786</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0893</v>
+        <v>-0.1194</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0893</v>
+        <v>-0.1194</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0893</v>
+        <v>-0.1194</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0893</v>
+        <v>-0.1194</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0893</v>
+        <v>-0.1194</v>
       </c>
       <c r="N29" t="n">
         <v>83</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1208</v>
+        <v>-0.1777</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.029</v>
+        <v>-0.0427</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6925</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1208</v>
+        <v>-0.1777</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1208</v>
+        <v>-0.1777</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1208</v>
+        <v>-0.1777</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1208</v>
+        <v>-0.1777</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1208</v>
+        <v>-0.1777</v>
       </c>
       <c r="N30" t="n">
         <v>136</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2004</v>
+        <v>-0.2071</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0481</v>
+        <v>-0.0497</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7285</v>
+        <v>-0.7185</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2004</v>
+        <v>-0.2071</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2004</v>
+        <v>-0.2071</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2004</v>
+        <v>-0.2071</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2004</v>
+        <v>-0.2071</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2004</v>
+        <v>-0.2071</v>
       </c>
       <c r="N31" t="n">
         <v>136</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.247</v>
+        <v>-0.269</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0593</v>
+        <v>-0.0646</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7467</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.247</v>
+        <v>-0.269</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.247</v>
+        <v>-0.269</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.247</v>
+        <v>-0.269</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.247</v>
+        <v>-0.269</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.247</v>
+        <v>-0.269</v>
       </c>
       <c r="N32" t="n">
         <v>83</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3044</v>
+        <v>-0.3361</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0731</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7754</v>
+        <v>-0.7772</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3044</v>
+        <v>-0.3361</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3044</v>
+        <v>-0.3361</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3044</v>
+        <v>-0.3361</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3044</v>
+        <v>-0.3361</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3044</v>
+        <v>-0.3361</v>
       </c>
       <c r="N33" t="n">
         <v>84</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3827</v>
+        <v>-0.4194</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0919</v>
+        <v>-0.1007</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8108</v>
+        <v>-0.8151</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3827</v>
+        <v>-0.4194</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3827</v>
+        <v>-0.4194</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3827</v>
+        <v>-0.4194</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3827</v>
+        <v>-0.4194</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3827</v>
+        <v>-0.4194</v>
       </c>
       <c r="N34" t="n">
         <v>84</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5855</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1406</v>
+        <v>-0.1335</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9023</v>
+        <v>-0.8773</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5855</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4181</v>
+        <v>-0.3802</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1674</v>
+        <v>-0.1757</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4181</v>
+        <v>-0.3802</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2174</v>
+        <v>-0.2053</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1674</v>
+        <v>-0.1757</v>
       </c>
       <c r="K35" t="n">
         <v>94</v>
@@ -2047,7 +2047,7 @@
         <v>73</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3848</v>
+        <v>-0.381</v>
       </c>
       <c r="N35" t="n">
         <v>167</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6564</v>
+        <v>-0.6267</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1576</v>
+        <v>-0.1505</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9343</v>
+        <v>-0.9095</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6564</v>
+        <v>-0.6267</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2983</v>
+        <v>-0.2522</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3581</v>
+        <v>-0.3745</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2983</v>
+        <v>-0.2522</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1551</v>
+        <v>-0.1362</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3581</v>
+        <v>-0.3745</v>
       </c>
       <c r="K36" t="n">
         <v>94</v>
@@ -2093,7 +2093,7 @@
         <v>73</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5132</v>
+        <v>-0.5106999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>167</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8313</v>
+        <v>-0.8764</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1996</v>
+        <v>-0.2104</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0133</v>
+        <v>-1.0232</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8313</v>
+        <v>-0.8764</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8313</v>
+        <v>-0.8764</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8313</v>
+        <v>-0.8764</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8313</v>
+        <v>-0.8764</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8313</v>
+        <v>-0.8764</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.842</v>
+        <v>-0.882</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2022</v>
+        <v>-0.2118</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0181</v>
+        <v>-1.0257</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.842</v>
+        <v>-0.882</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.842</v>
+        <v>-0.882</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.842</v>
+        <v>-0.882</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.842</v>
+        <v>-0.882</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.842</v>
+        <v>-0.882</v>
       </c>
       <c r="N38" t="n">
         <v>83</v>
@@ -2194,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9559</v>
+        <v>-0.9216</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2295</v>
+        <v>-0.2213</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0696</v>
+        <v>-1.0437</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9559</v>
+        <v>-0.9216</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.5352</v>
+        <v>-1.2782</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4207</v>
+        <v>0.3566</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5352</v>
+        <v>-1.2782</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2783</v>
+        <v>-0.6902</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4207</v>
+        <v>0.3566</v>
       </c>
       <c r="K39" t="n">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="L39" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.6990000000000001</v>
+        <v>-0.3336000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.161</v>
+        <v>-0.9574</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2788</v>
+        <v>-0.2299</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1621</v>
+        <v>-1.06</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.161</v>
+        <v>-0.9574</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.161</v>
+        <v>-0.5048</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.4526</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.161</v>
+        <v>-0.5048</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.161</v>
+        <v>-0.2726</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.4526</v>
       </c>
       <c r="K40" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.161</v>
+        <v>-0.7252000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2144</v>
+        <v>-1.1812</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2916</v>
+        <v>-0.2836</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1863</v>
+        <v>-1.1619</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2144</v>
+        <v>-1.1812</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4676</v>
+        <v>-1.1812</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2532</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4676</v>
+        <v>-1.1812</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7631</v>
+        <v>-1.1812</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2532</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L41" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.5099</v>
+        <v>-1.1812</v>
       </c>
       <c r="N41" t="n">
-        <v>290</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1699</v>
+        <v>1.1866</v>
       </c>
       <c r="J2" t="n">
-        <v>28.0776</v>
+        <v>28.4784</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0953</v>
+        <v>1.078</v>
       </c>
       <c r="J3" t="n">
-        <v>26.2872</v>
+        <v>25.872</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.638</v>
+        <v>0.6187</v>
       </c>
       <c r="J4" t="n">
-        <v>15.312</v>
+        <v>14.8488</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.542</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>13.008</v>
+        <v>12.7872</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.03</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0608</v>
+        <v>0.0876</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4592</v>
+        <v>2.1024</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2866</v>
+        <v>0.2818</v>
       </c>
       <c r="J7" t="n">
-        <v>6.8784</v>
+        <v>6.7632</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.037</v>
+        <v>-0.0482</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.888</v>
+        <v>-1.1568</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1535</v>
+        <v>-0.1699</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.684</v>
+        <v>-4.0776</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2436</v>
+        <v>-0.2602</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.8464</v>
+        <v>-6.2448</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3589</v>
+        <v>-0.3723</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.6136</v>
+        <v>-8.9352</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.87</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.117</v>
+        <v>-0.1416</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.34</v>
+        <v>-2.832</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2467</v>
+        <v>-0.2688</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.934</v>
+        <v>-5.376</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.64</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3486</v>
+        <v>-0.3677</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.972</v>
+        <v>-7.354</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3578</v>
+        <v>-0.3765</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.156</v>
+        <v>-7.53</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4791</v>
+        <v>-0.4912</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.582000000000001</v>
+        <v>-9.824</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7053</v>
+        <v>0.7069</v>
       </c>
       <c r="J17" t="n">
-        <v>14.106</v>
+        <v>14.138</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.56</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6542</v>
+        <v>0.6593</v>
       </c>
       <c r="J18" t="n">
-        <v>13.084</v>
+        <v>13.186</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4143</v>
+        <v>0.4317</v>
       </c>
       <c r="J19" t="n">
-        <v>8.286</v>
+        <v>8.634</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3463</v>
+        <v>0.3662</v>
       </c>
       <c r="J20" t="n">
-        <v>6.926</v>
+        <v>7.324</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2622</v>
+        <v>0.2844</v>
       </c>
       <c r="J21" t="n">
-        <v>5.244</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.19</v>
+        <v>1.2137</v>
       </c>
       <c r="J22" t="n">
-        <v>28.56</v>
+        <v>29.1288</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8679</v>
+        <v>0.8212</v>
       </c>
       <c r="J23" t="n">
-        <v>20.8296</v>
+        <v>19.7088</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.25</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6674</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>16.0176</v>
+        <v>15.4464</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5737</v>
+        <v>0.5597</v>
       </c>
       <c r="J25" t="n">
-        <v>13.7688</v>
+        <v>13.4328</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.96</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2322</v>
+        <v>-0.216</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.5728</v>
+        <v>-5.184</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3079</v>
+        <v>0.2975</v>
       </c>
       <c r="J27" t="n">
-        <v>7.3896</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1687</v>
+        <v>0.163</v>
       </c>
       <c r="J28" t="n">
-        <v>4.0488</v>
+        <v>3.912</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2376</v>
+        <v>-0.2555</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.7024</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.68</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3335</v>
+        <v>-0.349</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.004</v>
+        <v>-8.375999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4643</v>
+        <v>-0.4738</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.1432</v>
+        <v>-11.3712</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5033</v>
+        <v>0.5739</v>
       </c>
       <c r="J32" t="n">
-        <v>14.5957</v>
+        <v>16.6431</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3966</v>
+        <v>0.4464</v>
       </c>
       <c r="J33" t="n">
-        <v>11.5014</v>
+        <v>12.9456</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2852</v>
+        <v>0.3017</v>
       </c>
       <c r="J34" t="n">
-        <v>8.270799999999999</v>
+        <v>8.7493</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1513</v>
+        <v>-0.1603</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.3877</v>
+        <v>-4.6487</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1733</v>
+        <v>-0.1827</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.0257</v>
+        <v>-5.2983</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1571</v>
+        <v>0.1624</v>
       </c>
       <c r="J37" t="n">
-        <v>4.5559</v>
+        <v>4.7096</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.01</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0416</v>
+        <v>0.0433</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2064</v>
+        <v>1.2557</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1578</v>
+        <v>-0.1732</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.5762</v>
+        <v>-5.0228</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.8778</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2393</v>
+        <v>-0.2547</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.9397</v>
+        <v>-7.3863</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5083</v>
+        <v>0.5584</v>
       </c>
       <c r="J42" t="n">
-        <v>12.7075</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.92</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1018</v>
+        <v>-0.1161</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.545</v>
+        <v>-2.9025</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.91</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.113</v>
+        <v>-0.1277</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.825</v>
+        <v>-3.1925</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2259</v>
+        <v>-0.2422</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.6475</v>
+        <v>-6.055</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.463</v>
+        <v>-0.4713</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.575</v>
+        <v>-11.7825</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.48</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8335</v>
+        <v>0.9218</v>
       </c>
       <c r="J47" t="n">
-        <v>20.8375</v>
+        <v>23.045</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.41</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7436</v>
+        <v>0.8246</v>
       </c>
       <c r="J48" t="n">
-        <v>18.59</v>
+        <v>20.615</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4494</v>
+        <v>0.4982</v>
       </c>
       <c r="J49" t="n">
-        <v>11.235</v>
+        <v>12.455</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4051</v>
+        <v>0.4466</v>
       </c>
       <c r="J50" t="n">
-        <v>10.1275</v>
+        <v>11.165</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2599</v>
+        <v>-0.2439</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.4975</v>
+        <v>-6.0975</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.63</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2672</v>
+        <v>-0.3056</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.5424</v>
+        <v>-5.1952</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.39</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5252</v>
+        <v>-0.5425</v>
       </c>
       <c r="J53" t="n">
-        <v>-8.9284</v>
+        <v>-9.2225</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.37</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5441</v>
+        <v>-0.5598</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.249700000000001</v>
+        <v>-9.5166</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.33</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.584</v>
+        <v>-0.5961</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.928000000000001</v>
+        <v>-10.1337</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.3</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.615</v>
+        <v>-0.6241</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.455</v>
+        <v>-10.6097</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.27</v>
       </c>
       <c r="I57" t="n">
-        <v>1.6361</v>
+        <v>1.7848</v>
       </c>
       <c r="J57" t="n">
-        <v>27.8137</v>
+        <v>30.3416</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.77</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1042</v>
+        <v>1.2258</v>
       </c>
       <c r="J58" t="n">
-        <v>18.7714</v>
+        <v>20.8386</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.66</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9858</v>
+        <v>1.0985</v>
       </c>
       <c r="J59" t="n">
-        <v>16.7586</v>
+        <v>18.6745</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.47</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7649</v>
+        <v>0.8597</v>
       </c>
       <c r="J60" t="n">
-        <v>13.0033</v>
+        <v>14.6149</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.627</v>
+        <v>0.7089</v>
       </c>
       <c r="J61" t="n">
-        <v>10.659</v>
+        <v>12.0513</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.77</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6783</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>16.9575</v>
+        <v>19.4175</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2092</v>
+        <v>0.2268</v>
       </c>
       <c r="J63" t="n">
-        <v>5.23</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.09</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1406</v>
+        <v>0.1579</v>
       </c>
       <c r="J64" t="n">
-        <v>3.515</v>
+        <v>3.9475</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.094</v>
+        <v>-0.1001</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.35</v>
+        <v>-2.5025</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1185</v>
+        <v>-0.1258</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.9625</v>
+        <v>-3.145</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2959</v>
+        <v>0.2982</v>
       </c>
       <c r="J67" t="n">
-        <v>7.3975</v>
+        <v>7.455</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0094</v>
+        <v>0.0069</v>
       </c>
       <c r="J68" t="n">
-        <v>0.235</v>
+        <v>0.1725</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0824</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.06</v>
+        <v>-2.3675</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2208</v>
+        <v>-0.2361</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.52</v>
+        <v>-5.9025</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2801</v>
+        <v>-0.2945</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.0025</v>
+        <v>-7.3625</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5216</v>
+        <v>0.5664</v>
       </c>
       <c r="J72" t="n">
-        <v>11.9968</v>
+        <v>13.0272</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2904</v>
+        <v>-0.3082</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.6792</v>
+        <v>-7.0886</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.72</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2904</v>
+        <v>-0.3082</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.6792</v>
+        <v>-7.0886</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3189</v>
+        <v>-0.3358</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.3347</v>
+        <v>-7.7234</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4315</v>
+        <v>-0.4436</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.9245</v>
+        <v>-10.2028</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9025</v>
+        <v>0.9949</v>
       </c>
       <c r="J77" t="n">
-        <v>20.7575</v>
+        <v>22.8827</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7873</v>
+        <v>0.8709</v>
       </c>
       <c r="J78" t="n">
-        <v>18.1079</v>
+        <v>20.0307</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2415</v>
+        <v>0.2543</v>
       </c>
       <c r="J79" t="n">
-        <v>5.5545</v>
+        <v>5.8489</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2115</v>
+        <v>0.2263</v>
       </c>
       <c r="J80" t="n">
-        <v>4.8645</v>
+        <v>5.2049</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.95</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.254</v>
+        <v>-0.2397</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.842</v>
+        <v>-5.5131</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.15</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3581</v>
+        <v>0.368</v>
       </c>
       <c r="J82" t="n">
-        <v>8.952500000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0118</v>
+        <v>-0.0186</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.295</v>
+        <v>-0.465</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2083</v>
+        <v>-0.2242</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.2075</v>
+        <v>-5.605</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2184</v>
+        <v>-0.2342</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.46</v>
+        <v>-5.855</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2383</v>
+        <v>-0.254</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.9575</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.38</v>
       </c>
       <c r="I87" t="n">
-        <v>0.705</v>
+        <v>0.7824</v>
       </c>
       <c r="J87" t="n">
-        <v>17.625</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6392</v>
+        <v>0.7104</v>
       </c>
       <c r="J88" t="n">
-        <v>15.98</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.32</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6259</v>
+        <v>0.6958</v>
       </c>
       <c r="J89" t="n">
-        <v>15.6475</v>
+        <v>17.395</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.18</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4351</v>
+        <v>0.482</v>
       </c>
       <c r="J90" t="n">
-        <v>10.8775</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.191</v>
+        <v>-0.1778</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.775</v>
+        <v>-4.445</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.35</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.8686</v>
       </c>
       <c r="J92" t="n">
-        <v>26.0092</v>
+        <v>24.3208</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7664</v>
+        <v>0.7255</v>
       </c>
       <c r="J93" t="n">
-        <v>21.4592</v>
+        <v>20.314</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5728</v>
+        <v>0.5538</v>
       </c>
       <c r="J94" t="n">
-        <v>16.0384</v>
+        <v>15.5064</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J95" t="n">
-        <v>3.7828</v>
+        <v>4.1692</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6333</v>
+        <v>-0.5911</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.7324</v>
+        <v>-16.5508</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.213</v>
+        <v>0.2182</v>
       </c>
       <c r="J97" t="n">
-        <v>5.964</v>
+        <v>6.1096</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1464</v>
+        <v>0.153</v>
       </c>
       <c r="J98" t="n">
-        <v>4.0992</v>
+        <v>4.284</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0982</v>
+        <v>0.1046</v>
       </c>
       <c r="J99" t="n">
-        <v>2.7496</v>
+        <v>2.9288</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1525</v>
+        <v>-0.1665</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.27</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2352</v>
+        <v>-0.2495</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.5856</v>
+        <v>-6.986</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.12</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4561</v>
+        <v>0.4292</v>
       </c>
       <c r="J102" t="n">
-        <v>16.4196</v>
+        <v>15.4512</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0327</v>
+        <v>0.0225</v>
       </c>
       <c r="J103" t="n">
-        <v>1.1772</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.84</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4824</v>
+        <v>-0.4702</v>
       </c>
       <c r="J104" t="n">
-        <v>-17.3664</v>
+        <v>-16.9272</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.535</v>
+        <v>-0.5173</v>
       </c>
       <c r="J105" t="n">
-        <v>-19.26</v>
+        <v>-18.6228</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.68</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8891</v>
+        <v>-0.8279</v>
       </c>
       <c r="J106" t="n">
-        <v>-32.0076</v>
+        <v>-29.8044</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.7</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1039</v>
+        <v>1.0804</v>
       </c>
       <c r="J107" t="n">
-        <v>39.7404</v>
+        <v>38.8944</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4451</v>
+        <v>0.4491</v>
       </c>
       <c r="J108" t="n">
-        <v>16.0236</v>
+        <v>16.1676</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3265</v>
+        <v>0.3371</v>
       </c>
       <c r="J109" t="n">
-        <v>11.754</v>
+        <v>12.1356</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.04</v>
+        <v>-0.0403</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.44</v>
+        <v>-1.4508</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.121</v>
+        <v>-0.1278</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.356</v>
+        <v>-4.6008</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.32</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8848</v>
+        <v>0.8249</v>
       </c>
       <c r="J112" t="n">
-        <v>26.544</v>
+        <v>24.747</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.24</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6551</v>
       </c>
       <c r="J113" t="n">
-        <v>20.73</v>
+        <v>19.653</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.1</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3271</v>
+        <v>0.327</v>
       </c>
       <c r="J114" t="n">
-        <v>9.813000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.271</v>
+        <v>0.2746</v>
       </c>
       <c r="J115" t="n">
-        <v>8.130000000000001</v>
+        <v>8.238</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.0398</v>
+        <v>-0.9495</v>
       </c>
       <c r="J116" t="n">
-        <v>-31.194</v>
+        <v>-28.485</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6322</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>18.966</v>
+        <v>18.342</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.19</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4184</v>
+        <v>0.4152</v>
       </c>
       <c r="J118" t="n">
-        <v>12.552</v>
+        <v>12.456</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.03</v>
       </c>
       <c r="I119" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0993</v>
       </c>
       <c r="J119" t="n">
-        <v>2.724</v>
+        <v>2.979</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.77</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2695</v>
+        <v>-0.2823</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.085000000000001</v>
+        <v>-8.468999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.73</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3083</v>
+        <v>-0.3204</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.249000000000001</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.52</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1393</v>
+        <v>1.1073</v>
       </c>
       <c r="J122" t="n">
-        <v>28.4825</v>
+        <v>27.6825</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.47</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0775</v>
+        <v>1.0388</v>
       </c>
       <c r="J123" t="n">
-        <v>26.9375</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.42</v>
       </c>
       <c r="I124" t="n">
-        <v>1.0094</v>
+        <v>0.9595</v>
       </c>
       <c r="J124" t="n">
-        <v>25.235</v>
+        <v>23.9875</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.26</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6783</v>
+        <v>0.6558</v>
       </c>
       <c r="J125" t="n">
-        <v>16.9575</v>
+        <v>16.395</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.98</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1757</v>
+        <v>-0.1566</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.3925</v>
+        <v>-3.915</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5324</v>
+        <v>0.5029</v>
       </c>
       <c r="J127" t="n">
-        <v>13.31</v>
+        <v>12.5725</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.82</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.196</v>
+        <v>-0.2148</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.9</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.78</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2339</v>
+        <v>-0.2527</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.8475</v>
+        <v>-6.3175</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3948</v>
+        <v>-0.4086</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.869999999999999</v>
+        <v>-10.215</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4321</v>
+        <v>-0.444</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.8025</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.47</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0916</v>
+        <v>1.0519</v>
       </c>
       <c r="J132" t="n">
-        <v>30.5648</v>
+        <v>29.4532</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8925</v>
+        <v>0.8424</v>
       </c>
       <c r="J133" t="n">
-        <v>24.99</v>
+        <v>23.5872</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6908</v>
+        <v>0.6643</v>
       </c>
       <c r="J134" t="n">
-        <v>19.3424</v>
+        <v>18.6004</v>
       </c>
     </row>
     <row r="135">
@@ -7789,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0717</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>2.0076</v>
+        <v>2.6656</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4836</v>
+        <v>0.4702</v>
       </c>
       <c r="J137" t="n">
-        <v>13.5408</v>
+        <v>13.1656</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1803</v>
+        <v>0.1836</v>
       </c>
       <c r="J138" t="n">
-        <v>5.0484</v>
+        <v>5.1408</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1481</v>
+        <v>-0.1631</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.1468</v>
+        <v>-4.5668</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2304</v>
+        <v>-0.2457</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.4512</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3372</v>
+        <v>-0.3502</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.441599999999999</v>
+        <v>-9.8056</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.29</v>
       </c>
       <c r="I142" t="n">
-        <v>0.763</v>
+        <v>0.7275</v>
       </c>
       <c r="J142" t="n">
-        <v>20.601</v>
+        <v>19.6425</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7402</v>
+        <v>0.7074</v>
       </c>
       <c r="J143" t="n">
-        <v>19.9854</v>
+        <v>19.0998</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.24</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6486</v>
+        <v>0.6258</v>
       </c>
       <c r="J144" t="n">
-        <v>17.5122</v>
+        <v>16.8966</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.19</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5314</v>
+        <v>0.5204</v>
       </c>
       <c r="J145" t="n">
-        <v>14.3478</v>
+        <v>14.0508</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4307</v>
+        <v>0.4292</v>
       </c>
       <c r="J146" t="n">
-        <v>11.6289</v>
+        <v>11.5884</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7758</v>
+        <v>0.7317</v>
       </c>
       <c r="J147" t="n">
-        <v>20.9466</v>
+        <v>19.7559</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.9</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1235</v>
+        <v>-0.1387</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.3345</v>
+        <v>-3.7449</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.85</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.175</v>
+        <v>-0.1915</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.725</v>
+        <v>-5.1705</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3416</v>
+        <v>-0.3554</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.2232</v>
+        <v>-9.595800000000001</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3699</v>
+        <v>-0.3826</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.987299999999999</v>
+        <v>-10.3302</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.15</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3863</v>
+        <v>0.3765</v>
       </c>
       <c r="J152" t="n">
-        <v>11.589</v>
+        <v>11.295</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2619</v>
+        <v>0.259</v>
       </c>
       <c r="J153" t="n">
-        <v>7.857</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1122</v>
+        <v>-0.1271</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.366</v>
+        <v>-3.813</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.73</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2933</v>
+        <v>-0.3086</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.798999999999999</v>
+        <v>-9.257999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4712</v>
+        <v>-0.4793</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.136</v>
+        <v>-14.379</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.22</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6197</v>
+        <v>0.5962</v>
       </c>
       <c r="J157" t="n">
-        <v>18.591</v>
+        <v>17.886</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5744</v>
       </c>
       <c r="J158" t="n">
-        <v>17.859</v>
+        <v>17.232</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.19</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5461</v>
+        <v>0.5303</v>
       </c>
       <c r="J159" t="n">
-        <v>16.383</v>
+        <v>15.909</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4715</v>
+        <v>0.4627</v>
       </c>
       <c r="J160" t="n">
-        <v>14.145</v>
+        <v>13.881</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2682</v>
+        <v>-0.2577</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.045999999999999</v>
+        <v>-7.731</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.25</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5298</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J162" t="n">
-        <v>15.3642</v>
+        <v>15.0104</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4759</v>
+        <v>0.468</v>
       </c>
       <c r="J163" t="n">
-        <v>13.8011</v>
+        <v>13.572</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0204</v>
+        <v>-0.0251</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.5916</v>
+        <v>-0.7279</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2488</v>
+        <v>-0.2621</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.2152</v>
+        <v>-7.6009</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2977</v>
+        <v>-0.3102</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.6333</v>
+        <v>-8.995799999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1894</v>
+        <v>1.1515</v>
       </c>
       <c r="J167" t="n">
-        <v>34.4926</v>
+        <v>33.3935</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.602</v>
+        <v>0.579</v>
       </c>
       <c r="J168" t="n">
-        <v>17.458</v>
+        <v>16.791</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2035</v>
+        <v>0.213</v>
       </c>
       <c r="J169" t="n">
-        <v>5.9015</v>
+        <v>6.177</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.01</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0267</v>
+        <v>0.0404</v>
       </c>
       <c r="J170" t="n">
-        <v>0.7743</v>
+        <v>1.1716</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6551</v>
+        <v>-0.6113</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.9979</v>
+        <v>-17.7277</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1388</v>
+        <v>1.097</v>
       </c>
       <c r="J172" t="n">
-        <v>67.1892</v>
+        <v>64.723</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2933</v>
+        <v>0.2971</v>
       </c>
       <c r="J173" t="n">
-        <v>17.3047</v>
+        <v>17.5289</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.02</v>
       </c>
       <c r="I174" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="J174" t="n">
-        <v>4.0769</v>
+        <v>4.8852</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0265</v>
+        <v>-0.0182</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.5635</v>
+        <v>-1.0738</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1224</v>
+        <v>-0.1193</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.2216</v>
+        <v>-7.0387</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.27</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5568</v>
+        <v>0.5438</v>
       </c>
       <c r="J177" t="n">
-        <v>32.8512</v>
+        <v>32.0842</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.08</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2001</v>
+        <v>0.209</v>
       </c>
       <c r="J178" t="n">
-        <v>11.8059</v>
+        <v>12.331</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0354</v>
+        <v>0.0417</v>
       </c>
       <c r="J179" t="n">
-        <v>2.0886</v>
+        <v>2.4603</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0223</v>
+        <v>-0.0266</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.3157</v>
+        <v>-1.5694</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2811</v>
+        <v>-0.2934</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.5849</v>
+        <v>-17.3106</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8563</v>
+        <v>0.802</v>
       </c>
       <c r="J182" t="n">
-        <v>22.2638</v>
+        <v>20.852</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1258</v>
+        <v>0.1246</v>
       </c>
       <c r="J183" t="n">
-        <v>3.2708</v>
+        <v>3.2396</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.93</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0877</v>
+        <v>-0.1021</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.2802</v>
+        <v>-2.6546</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4881</v>
+        <v>-0.4954</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.6906</v>
+        <v>-12.8804</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.48</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5245</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.637</v>
+        <v>-13.7722</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.67</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3484</v>
+        <v>1.3258</v>
       </c>
       <c r="J187" t="n">
-        <v>35.0584</v>
+        <v>34.4708</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.25</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6725</v>
+        <v>0.647</v>
       </c>
       <c r="J188" t="n">
-        <v>17.485</v>
+        <v>16.822</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3523</v>
+        <v>0.3574</v>
       </c>
       <c r="J189" t="n">
-        <v>9.159800000000001</v>
+        <v>9.292400000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2683</v>
+        <v>0.2799</v>
       </c>
       <c r="J190" t="n">
-        <v>6.9758</v>
+        <v>7.2774</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.99</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1095</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.847</v>
+        <v>-2.5376</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.28</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7719</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="J192" t="n">
-        <v>21.6132</v>
+        <v>20.4204</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.26</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7239</v>
+        <v>0.6871</v>
       </c>
       <c r="J193" t="n">
-        <v>20.2692</v>
+        <v>19.2388</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6511</v>
+        <v>0.6227</v>
       </c>
       <c r="J194" t="n">
-        <v>18.2308</v>
+        <v>17.4356</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.2</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5772</v>
+        <v>0.5568</v>
       </c>
       <c r="J195" t="n">
-        <v>16.1616</v>
+        <v>15.5904</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.63</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.0741</v>
+        <v>-0.9774</v>
       </c>
       <c r="J196" t="n">
-        <v>-30.0748</v>
+        <v>-27.3672</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.2</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4467</v>
+        <v>0.4396</v>
       </c>
       <c r="J197" t="n">
-        <v>12.5076</v>
+        <v>12.3088</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3714</v>
+        <v>0.3695</v>
       </c>
       <c r="J198" t="n">
-        <v>10.3992</v>
+        <v>10.346</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0857</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.3996</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1641</v>
+        <v>-0.1781</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5948</v>
+        <v>-4.9868</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.324</v>
+        <v>-0.3363</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.071999999999999</v>
+        <v>-9.416399999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.83</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1791</v>
+        <v>-0.1995</v>
       </c>
       <c r="J202" t="n">
-        <v>-3.9402</v>
+        <v>-4.389</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.83</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1791</v>
+        <v>-0.1995</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.9402</v>
+        <v>-4.389</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2392</v>
+        <v>-0.2589</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.2624</v>
+        <v>-5.6958</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2575</v>
+        <v>-0.277</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.665</v>
+        <v>-6.094</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4162</v>
+        <v>-0.4301</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.1564</v>
+        <v>-9.462199999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.61</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2513</v>
+        <v>1.2269</v>
       </c>
       <c r="J207" t="n">
-        <v>27.5286</v>
+        <v>26.9918</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0404</v>
+        <v>0.9944</v>
       </c>
       <c r="J208" t="n">
-        <v>22.8888</v>
+        <v>21.8768</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.38</v>
       </c>
       <c r="I209" t="n">
-        <v>0.9402</v>
+        <v>0.8887</v>
       </c>
       <c r="J209" t="n">
-        <v>20.6844</v>
+        <v>19.5514</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4621</v>
+        <v>0.4619</v>
       </c>
       <c r="J210" t="n">
-        <v>10.1662</v>
+        <v>10.1618</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.0774</v>
+        <v>-0.0537</v>
       </c>
       <c r="J211" t="n">
-        <v>-1.7028</v>
+        <v>-1.1814</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.26</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5491</v>
+        <v>0.535</v>
       </c>
       <c r="J212" t="n">
-        <v>19.2185</v>
+        <v>18.725</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2479</v>
+        <v>0.2536</v>
       </c>
       <c r="J213" t="n">
-        <v>8.676500000000001</v>
+        <v>8.875999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0994</v>
+        <v>-0.111</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.479</v>
+        <v>-3.885</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1336</v>
+        <v>-0.1464</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.676</v>
+        <v>-5.124</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2582</v>
+        <v>-0.2715</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.037000000000001</v>
+        <v>-9.5025</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.47</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1298</v>
+        <v>1.0865</v>
       </c>
       <c r="J217" t="n">
-        <v>39.543</v>
+        <v>38.0275</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4555</v>
+        <v>0.446</v>
       </c>
       <c r="J218" t="n">
-        <v>15.9425</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1559</v>
+        <v>-0.1533</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.4565</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1909</v>
+        <v>-0.1871</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.6815</v>
+        <v>-6.5485</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2242</v>
+        <v>-0.219</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.847</v>
+        <v>-7.665</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.37</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9379</v>
+        <v>0.883</v>
       </c>
       <c r="J222" t="n">
-        <v>23.4475</v>
+        <v>22.075</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.783</v>
+        <v>0.7457</v>
       </c>
       <c r="J223" t="n">
-        <v>19.575</v>
+        <v>18.6425</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.22</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6012</v>
+        <v>0.5836</v>
       </c>
       <c r="J224" t="n">
-        <v>15.03</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.18</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5043</v>
+        <v>0.4964</v>
       </c>
       <c r="J225" t="n">
-        <v>12.6075</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4018</v>
+        <v>0.4035</v>
       </c>
       <c r="J226" t="n">
-        <v>10.045</v>
+        <v>10.0875</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.11</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3191</v>
+        <v>0.3103</v>
       </c>
       <c r="J227" t="n">
-        <v>7.9775</v>
+        <v>7.7575</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.89</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1302</v>
+        <v>-0.1467</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.255</v>
+        <v>-3.6675</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2403</v>
+        <v>-0.2576</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.0075</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.77</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2501</v>
+        <v>-0.2672</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.2525</v>
+        <v>-6.68</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3175</v>
+        <v>-0.333</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.9375</v>
+        <v>-8.324999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2569/event_2569_evp_summary.xlsx
+++ b/database/event/2569/event_2569_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3264</v>
+        <v>5.2592</v>
       </c>
       <c r="C2" t="n">
-        <v>1.279</v>
+        <v>1.2628</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8005</v>
+        <v>1.79</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3264</v>
+        <v>5.2592</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9266</v>
+        <v>2.8855</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3998</v>
+        <v>2.3737</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7617</v>
+        <v>4.3908</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5713</v>
+        <v>2.4653</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3998</v>
+        <v>2.3737</v>
       </c>
       <c r="K2" t="n">
         <v>106</v>
@@ -529,7 +529,7 @@
         <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9711</v>
+        <v>4.839</v>
       </c>
       <c r="N2" t="n">
         <v>247</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6304</v>
+        <v>4.4158</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1118</v>
+        <v>1.0603</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4836</v>
+        <v>1.4058</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6304</v>
+        <v>4.4158</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8228</v>
+        <v>3.0826</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8076</v>
+        <v>1.3332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8228</v>
+        <v>5.1307</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9843</v>
+        <v>2.8807</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8076</v>
+        <v>1.3332</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7919</v>
+        <v>4.2139</v>
       </c>
       <c r="N3" t="n">
         <v>247</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4937</v>
+        <v>4.3568</v>
       </c>
       <c r="C4" t="n">
-        <v>1.079</v>
+        <v>1.0461</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4214</v>
+        <v>1.3789</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4937</v>
+        <v>4.3568</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1334</v>
+        <v>1.5817</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3603</v>
+        <v>2.7751</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4442</v>
+        <v>1.5817</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9398</v>
+        <v>0.8881</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3603</v>
+        <v>2.7751</v>
       </c>
       <c r="K4" t="n">
         <v>106</v>
@@ -621,7 +621,7 @@
         <v>141</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3001</v>
+        <v>3.6632</v>
       </c>
       <c r="N4" t="n">
         <v>247</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0916</v>
+        <v>3.9015</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9825</v>
+        <v>0.9368</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2384</v>
+        <v>1.1715</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0916</v>
+        <v>3.9015</v>
       </c>
       <c r="F5" t="n">
-        <v>1.573</v>
+        <v>1.376</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5187</v>
+        <v>2.5254</v>
       </c>
       <c r="H5" t="n">
-        <v>1.573</v>
+        <v>1.376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8494</v>
+        <v>0.7726</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5187</v>
+        <v>2.5254</v>
       </c>
       <c r="K5" t="n">
         <v>151</v>
@@ -667,7 +667,7 @@
         <v>139</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3681</v>
+        <v>3.298</v>
       </c>
       <c r="N5" t="n">
         <v>290</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9837</v>
+        <v>3.7844</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9566</v>
+        <v>0.9087</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1893</v>
+        <v>1.1182</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9837</v>
+        <v>3.7844</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7545</v>
+        <v>1.6704</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2292</v>
+        <v>2.114</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7545</v>
+        <v>1.6704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9474</v>
+        <v>0.9379</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2292</v>
+        <v>2.114</v>
       </c>
       <c r="K6" t="n">
         <v>151</v>
@@ -713,7 +713,7 @@
         <v>139</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1766</v>
+        <v>3.0519</v>
       </c>
       <c r="N6" t="n">
         <v>290</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3841</v>
+        <v>3.4266</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8126</v>
+        <v>0.8228</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9163</v>
+        <v>0.9552</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3841</v>
+        <v>3.4266</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3354</v>
+        <v>2.361</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0487</v>
+        <v>1.0656</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3354</v>
+        <v>2.4215</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7211</v>
+        <v>1.3596</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0487</v>
+        <v>1.0656</v>
       </c>
       <c r="K7" t="n">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="L7" t="n">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7698</v>
+        <v>2.4252</v>
       </c>
       <c r="N7" t="n">
-        <v>290</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3689</v>
+        <v>2.9594</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8089</v>
+        <v>0.7106</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9094</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3689</v>
+        <v>2.9594</v>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>1.0556</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1089</v>
+        <v>1.9038</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5623</v>
+        <v>1.0556</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3836</v>
+        <v>0.5927</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1089</v>
+        <v>1.9038</v>
       </c>
       <c r="K8" t="n">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="L8" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4925</v>
+        <v>2.4965</v>
       </c>
       <c r="N8" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8691</v>
+        <v>2.7893</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6889</v>
+        <v>0.6698</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6819</v>
+        <v>0.6649</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8691</v>
+        <v>2.7893</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1246</v>
+        <v>0.8136</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7445</v>
+        <v>1.9757</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1246</v>
+        <v>0.8136</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6073</v>
+        <v>0.4568</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7445</v>
+        <v>1.9757</v>
       </c>
       <c r="K9" t="n">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="L9" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3518</v>
+        <v>2.4325</v>
       </c>
       <c r="N9" t="n">
-        <v>290</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8497</v>
+        <v>2.6623</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6843</v>
+        <v>0.6393</v>
       </c>
       <c r="D10" t="n">
-        <v>0.673</v>
+        <v>0.607</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8497</v>
+        <v>2.6623</v>
       </c>
       <c r="F10" t="n">
-        <v>0.925</v>
+        <v>1.0052</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9247</v>
+        <v>1.6571</v>
       </c>
       <c r="H10" t="n">
-        <v>0.925</v>
+        <v>1.0052</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4995</v>
+        <v>0.5644</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9247</v>
+        <v>1.6571</v>
       </c>
       <c r="K10" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="L10" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4242</v>
+        <v>2.2215</v>
       </c>
       <c r="N10" t="n">
-        <v>247</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4327</v>
+        <v>2.3864</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5841</v>
+        <v>0.573</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4832</v>
+        <v>0.4813</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4327</v>
+        <v>2.3864</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4327</v>
+        <v>2.3864</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5994</v>
+        <v>2.5187</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5994</v>
+        <v>2.5187</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5994</v>
+        <v>2.5187</v>
       </c>
       <c r="N11" t="n">
         <v>154</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4314</v>
+        <v>2.3679</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5838</v>
+        <v>0.5686</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4826</v>
+        <v>0.4729</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4314</v>
+        <v>2.3679</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4314</v>
+        <v>2.3679</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5966</v>
+        <v>2.4763</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5966</v>
+        <v>2.4763</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5966</v>
+        <v>2.4763</v>
       </c>
       <c r="N12" t="n">
         <v>136</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2041</v>
+        <v>2.1756</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5292</v>
+        <v>0.5224</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3791</v>
+        <v>0.3853</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2041</v>
+        <v>2.1756</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9162</v>
+        <v>2.9448</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7121</v>
+        <v>-0.7692</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7273</v>
+        <v>4.6134</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5527</v>
+        <v>2.5903</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7121</v>
+        <v>-0.7692</v>
       </c>
       <c r="K13" t="n">
         <v>48</v>
@@ -1035,7 +1035,7 @@
         <v>71</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8406</v>
+        <v>1.8211</v>
       </c>
       <c r="N13" t="n">
         <v>119</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0773</v>
+        <v>2.0625</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4988</v>
+        <v>0.4952</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3214</v>
+        <v>0.3338</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0773</v>
+        <v>2.0625</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0773</v>
+        <v>2.4347</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.3722</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0773</v>
+        <v>2.6983</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0773</v>
+        <v>1.515</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.3722</v>
       </c>
       <c r="K14" t="n">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0773</v>
+        <v>1.1428</v>
       </c>
       <c r="N14" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9864</v>
+        <v>1.9299</v>
       </c>
       <c r="C15" t="n">
-        <v>0.477</v>
+        <v>0.4634</v>
       </c>
       <c r="D15" t="n">
-        <v>0.28</v>
+        <v>0.2734</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9864</v>
+        <v>1.9299</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3494</v>
+        <v>1.9299</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.363</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8575</v>
+        <v>1.9299</v>
       </c>
       <c r="I15" t="n">
-        <v>1.543</v>
+        <v>1.9299</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.363</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="L15" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.18</v>
+        <v>1.9299</v>
       </c>
       <c r="N15" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8774</v>
+        <v>1.7752</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4508</v>
+        <v>0.4263</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2304</v>
+        <v>0.2029</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8774</v>
+        <v>1.7752</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2104</v>
+        <v>1.1486</v>
       </c>
       <c r="G16" t="n">
-        <v>0.667</v>
+        <v>0.6266</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2104</v>
+        <v>1.1486</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6536</v>
+        <v>0.6449</v>
       </c>
       <c r="J16" t="n">
-        <v>0.667</v>
+        <v>0.6266</v>
       </c>
       <c r="K16" t="n">
         <v>106</v>
@@ -1173,7 +1173,7 @@
         <v>141</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3206</v>
+        <v>1.2715</v>
       </c>
       <c r="N16" t="n">
         <v>247</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7248</v>
+        <v>1.5883</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4142</v>
+        <v>0.3814</v>
       </c>
       <c r="D17" t="n">
-        <v>0.161</v>
+        <v>0.1178</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7248</v>
+        <v>1.5883</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7248</v>
+        <v>1.5883</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7248</v>
+        <v>1.5883</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7248</v>
+        <v>1.5883</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7248</v>
+        <v>1.5883</v>
       </c>
       <c r="N17" t="n">
         <v>154</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4991</v>
+        <v>1.4614</v>
       </c>
       <c r="C18" t="n">
-        <v>0.36</v>
+        <v>0.3509</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0582</v>
+        <v>0.0599</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4991</v>
+        <v>1.4614</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6608</v>
+        <v>1.6329</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1617</v>
+        <v>-0.1715</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6608</v>
+        <v>1.6329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8968</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1617</v>
+        <v>-0.1715</v>
       </c>
       <c r="K18" t="n">
         <v>48</v>
@@ -1265,7 +1265,7 @@
         <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7351000000000001</v>
+        <v>0.7453</v>
       </c>
       <c r="N18" t="n">
         <v>119</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3453</v>
+        <v>1.4238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.323</v>
+        <v>0.3419</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0118</v>
+        <v>0.0428</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3453</v>
+        <v>1.4238</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3453</v>
+        <v>2.4238</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8439</v>
+        <v>2.6573</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5357</v>
+        <v>1.492</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>71</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5357000000000001</v>
+        <v>0.492</v>
       </c>
       <c r="N19" t="n">
         <v>119</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lukki</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1548</v>
+        <v>1.0123</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2773</v>
+        <v>0.2431</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0985</v>
+        <v>-0.1446</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1548</v>
+        <v>1.0123</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1548</v>
+        <v>1.0123</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1548</v>
+        <v>1.0123</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1548</v>
+        <v>1.0123</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1548</v>
+        <v>1.0123</v>
       </c>
       <c r="N20" t="n">
-        <v>84</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Lukki</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0963</v>
+        <v>0.9879</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2632</v>
+        <v>0.2372</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1251</v>
+        <v>-0.1558</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0963</v>
+        <v>0.9879</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3737</v>
+        <v>0.9879</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2774</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3737</v>
+        <v>0.9879</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7418</v>
+        <v>0.9879</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2774</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="L21" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4644</v>
+        <v>0.9879</v>
       </c>
       <c r="N21" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0712</v>
+        <v>0.8776</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2572</v>
+        <v>0.2107</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1366</v>
+        <v>-0.206</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0712</v>
+        <v>0.8776</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0712</v>
+        <v>1.2099</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.3323</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0712</v>
+        <v>1.2099</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0712</v>
+        <v>0.6793</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.3323</v>
       </c>
       <c r="K22" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0712</v>
+        <v>0.347</v>
       </c>
       <c r="N22" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9256</v>
+        <v>0.8348</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2223</v>
+        <v>0.2005</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2029</v>
+        <v>-0.2255</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9256</v>
+        <v>0.8348</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9256</v>
+        <v>0.8348</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9256</v>
+        <v>0.8348</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9256</v>
+        <v>0.8348</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9256</v>
+        <v>0.8348</v>
       </c>
       <c r="N23" t="n">
         <v>83</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7146</v>
+        <v>0.641</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1716</v>
+        <v>0.1539</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2989</v>
+        <v>-0.3138</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7146</v>
+        <v>0.641</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5624</v>
+        <v>0.4893</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1522</v>
+        <v>0.1517</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5624</v>
+        <v>0.4893</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3037</v>
+        <v>0.2747</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1522</v>
+        <v>0.1517</v>
       </c>
       <c r="K24" t="n">
         <v>48</v>
@@ -1541,7 +1541,7 @@
         <v>71</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4559</v>
+        <v>0.4264</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6352</v>
+        <v>0.5845</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1525</v>
+        <v>0.1403</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.335</v>
+        <v>-0.3395</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6352</v>
+        <v>0.5845</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6352</v>
+        <v>0.5845</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6352</v>
+        <v>0.5845</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6352</v>
+        <v>0.5845</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6352</v>
+        <v>0.5845</v>
       </c>
       <c r="N25" t="n">
         <v>154</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5889</v>
+        <v>0.5163</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1414</v>
+        <v>0.124</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3561</v>
+        <v>-0.3706</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5889</v>
+        <v>0.5163</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5889</v>
+        <v>0.5163</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5889</v>
+        <v>0.5163</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5889</v>
+        <v>0.5163</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5889</v>
+        <v>0.5163</v>
       </c>
       <c r="N26" t="n">
         <v>136</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1006</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0242</v>
+        <v>0.0196</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5784</v>
+        <v>-0.5686</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1006</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1006</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1006</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1006</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1006</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>83</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ryxxo</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1084</v>
+        <v>-0.1443</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.026</v>
+        <v>-0.0346</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6735</v>
+        <v>-0.6715</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1084</v>
+        <v>-0.1443</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1084</v>
+        <v>-0.1443</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1084</v>
+        <v>-0.1443</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1084</v>
+        <v>-0.1443</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1084</v>
+        <v>-0.1443</v>
       </c>
       <c r="N28" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>Ryxxo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1194</v>
+        <v>-0.1484</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0287</v>
+        <v>-0.0356</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6786</v>
+        <v>-0.6734</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1194</v>
+        <v>-0.1484</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1194</v>
+        <v>-0.1484</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1194</v>
+        <v>-0.1484</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1194</v>
+        <v>-0.1484</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1194</v>
+        <v>-0.1484</v>
       </c>
       <c r="N29" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1777</v>
+        <v>-0.1993</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0427</v>
+        <v>-0.0479</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.6966</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1777</v>
+        <v>-0.1993</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1777</v>
+        <v>-0.1993</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1777</v>
+        <v>-0.1993</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1777</v>
+        <v>-0.1993</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1777</v>
+        <v>-0.1993</v>
       </c>
       <c r="N30" t="n">
         <v>136</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2071</v>
+        <v>-0.2331</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0497</v>
+        <v>-0.056</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7185</v>
+        <v>-0.712</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2071</v>
+        <v>-0.2331</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2071</v>
+        <v>-0.2331</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2071</v>
+        <v>-0.2331</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2071</v>
+        <v>-0.2331</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2071</v>
+        <v>-0.2331</v>
       </c>
       <c r="N31" t="n">
         <v>136</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.269</v>
+        <v>-0.2774</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0646</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7467</v>
+        <v>-0.7322</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.269</v>
+        <v>-0.2774</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.269</v>
+        <v>-0.2774</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.269</v>
+        <v>-0.2774</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.269</v>
+        <v>-0.2774</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.269</v>
+        <v>-0.2774</v>
       </c>
       <c r="N32" t="n">
         <v>83</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3361</v>
+        <v>-0.3467</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0832</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7772</v>
+        <v>-0.7637</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3361</v>
+        <v>-0.3467</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3361</v>
+        <v>-0.3467</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3361</v>
+        <v>-0.3467</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3361</v>
+        <v>-0.3467</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3361</v>
+        <v>-0.3467</v>
       </c>
       <c r="N33" t="n">
         <v>84</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4194</v>
+        <v>-0.3775</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1007</v>
+        <v>-0.0906</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8151</v>
+        <v>-0.7778</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4194</v>
+        <v>-0.3775</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4194</v>
+        <v>-0.3775</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4194</v>
+        <v>-0.3775</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4194</v>
+        <v>-0.3775</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4194</v>
+        <v>-0.3775</v>
       </c>
       <c r="N34" t="n">
         <v>84</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1335</v>
+        <v>-0.1202</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8773</v>
+        <v>-0.8338</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3802</v>
+        <v>-0.2955</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1757</v>
+        <v>-0.205</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3802</v>
+        <v>-0.2955</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2053</v>
+        <v>-0.1659</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1757</v>
+        <v>-0.205</v>
       </c>
       <c r="K35" t="n">
         <v>94</v>
@@ -2047,7 +2047,7 @@
         <v>73</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.381</v>
+        <v>-0.3709</v>
       </c>
       <c r="N35" t="n">
         <v>167</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6267</v>
+        <v>-0.5804</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1505</v>
+        <v>-0.1394</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9095</v>
+        <v>-0.8702</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6267</v>
+        <v>-0.5804</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2522</v>
+        <v>-0.2077</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3745</v>
+        <v>-0.3727</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2522</v>
+        <v>-0.2077</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1362</v>
+        <v>-0.1166</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3745</v>
+        <v>-0.3727</v>
       </c>
       <c r="K36" t="n">
         <v>94</v>
@@ -2093,7 +2093,7 @@
         <v>73</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5106999999999999</v>
+        <v>-0.4893</v>
       </c>
       <c r="N36" t="n">
         <v>167</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8764</v>
+        <v>-0.7947</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2104</v>
+        <v>-0.1908</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0232</v>
+        <v>-0.9678</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8764</v>
+        <v>-0.7947</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8764</v>
+        <v>-0.382</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.4127</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8764</v>
+        <v>-0.382</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8764</v>
+        <v>-0.2145</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.4127</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8764</v>
+        <v>-0.6272</v>
       </c>
       <c r="N37" t="n">
-        <v>84</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.882</v>
+        <v>-0.8027</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2118</v>
+        <v>-0.1927</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0257</v>
+        <v>-0.9715</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.882</v>
+        <v>-0.8027</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.882</v>
+        <v>-1.202</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.3993</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.882</v>
+        <v>-1.202</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.882</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.3993</v>
       </c>
       <c r="K38" t="n">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.882</v>
+        <v>-0.2756000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>83</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Console</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9216</v>
+        <v>-0.8227</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2213</v>
+        <v>-0.1975</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0437</v>
+        <v>-0.9806</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9216</v>
+        <v>-0.8227</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2782</v>
+        <v>-0.8227</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3566</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2782</v>
+        <v>-0.8227</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6902</v>
+        <v>-0.8227</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3566</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="L39" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.3336000000000001</v>
+        <v>-0.8227</v>
       </c>
       <c r="N39" t="n">
-        <v>290</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9574</v>
+        <v>-0.8341</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2299</v>
+        <v>-0.2003</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.06</v>
+        <v>-0.9858</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9574</v>
+        <v>-0.8341</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5048</v>
+        <v>-0.8341</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4526</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5048</v>
+        <v>-0.8341</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2726</v>
+        <v>-0.8341</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4526</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="L40" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.7252000000000001</v>
+        <v>-0.8341</v>
       </c>
       <c r="N40" t="n">
-        <v>167</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.1812</v>
+        <v>-1.113</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2836</v>
+        <v>-0.2673</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1619</v>
+        <v>-1.1128</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.1812</v>
+        <v>-1.113</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1812</v>
+        <v>-1.113</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1812</v>
+        <v>-1.113</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1812</v>
+        <v>-1.113</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1812</v>
+        <v>-1.113</v>
       </c>
       <c r="N41" t="n">
         <v>136</v>
@@ -2429,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1866</v>
+        <v>1.2006</v>
       </c>
       <c r="J2" t="n">
-        <v>28.4784</v>
+        <v>28.8144</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>1.078</v>
+        <v>1.08</v>
       </c>
       <c r="J3" t="n">
-        <v>25.872</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6187</v>
+        <v>0.591</v>
       </c>
       <c r="J4" t="n">
-        <v>14.8488</v>
+        <v>14.184</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5027</v>
       </c>
       <c r="J5" t="n">
-        <v>12.7872</v>
+        <v>12.0648</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.03</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0876</v>
+        <v>0.0668</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1024</v>
+        <v>1.6032</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2818</v>
+        <v>0.234</v>
       </c>
       <c r="J7" t="n">
-        <v>6.7632</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0482</v>
+        <v>-0.0387</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1568</v>
+        <v>-0.9288</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1699</v>
+        <v>-0.1517</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.0776</v>
+        <v>-3.6408</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2602</v>
+        <v>-0.241</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.2448</v>
+        <v>-5.784</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3723</v>
+        <v>-0.3587</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.9352</v>
+        <v>-8.6088</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.87</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1416</v>
+        <v>-0.1249</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.832</v>
+        <v>-2.498</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.75</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2688</v>
+        <v>-0.2551</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.376</v>
+        <v>-5.102</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.64</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3677</v>
+        <v>-0.3558</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.354</v>
+        <v>-7.116</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3765</v>
+        <v>-0.3649</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.53</v>
+        <v>-7.298</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4912</v>
+        <v>-0.4883</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.824</v>
+        <v>-9.766</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.61</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7069</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>14.138</v>
+        <v>12.712</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.56</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6593</v>
+        <v>0.5888</v>
       </c>
       <c r="J18" t="n">
-        <v>13.186</v>
+        <v>11.776</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.33</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4317</v>
+        <v>0.3722</v>
       </c>
       <c r="J19" t="n">
-        <v>8.634</v>
+        <v>7.444</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3662</v>
+        <v>0.3114</v>
       </c>
       <c r="J20" t="n">
-        <v>7.324</v>
+        <v>6.228</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2844</v>
+        <v>0.2364</v>
       </c>
       <c r="J21" t="n">
-        <v>5.688</v>
+        <v>4.728</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2137</v>
+        <v>1.2305</v>
       </c>
       <c r="J22" t="n">
-        <v>29.1288</v>
+        <v>29.532</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8212</v>
+        <v>0.8008</v>
       </c>
       <c r="J23" t="n">
-        <v>19.7088</v>
+        <v>19.2192</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.25</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="J24" t="n">
-        <v>15.4464</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5597</v>
+        <v>0.5289</v>
       </c>
       <c r="J25" t="n">
-        <v>13.4328</v>
+        <v>12.6936</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.96</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.216</v>
+        <v>-0.1826</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.184</v>
+        <v>-4.3824</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2975</v>
+        <v>0.2511</v>
       </c>
       <c r="J27" t="n">
-        <v>7.14</v>
+        <v>6.0264</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.163</v>
+        <v>0.129</v>
       </c>
       <c r="J28" t="n">
-        <v>3.912</v>
+        <v>3.096</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2555</v>
+        <v>-0.2371</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.132</v>
+        <v>-5.6904</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.68</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.349</v>
+        <v>-0.3338</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.375999999999999</v>
+        <v>-8.011200000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4738</v>
+        <v>-0.4699</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.3712</v>
+        <v>-11.2776</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.49</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5739</v>
+        <v>0.5386</v>
       </c>
       <c r="J32" t="n">
-        <v>16.6431</v>
+        <v>15.6194</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4464</v>
+        <v>0.3852</v>
       </c>
       <c r="J33" t="n">
-        <v>12.9456</v>
+        <v>11.1708</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3017</v>
+        <v>0.2479</v>
       </c>
       <c r="J34" t="n">
-        <v>8.7493</v>
+        <v>7.1891</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1603</v>
+        <v>-0.1405</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.6487</v>
+        <v>-4.0745</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1827</v>
+        <v>-0.1627</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.2983</v>
+        <v>-4.7183</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1624</v>
+        <v>0.1452</v>
       </c>
       <c r="J37" t="n">
-        <v>4.7096</v>
+        <v>4.2108</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.01</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0433</v>
+        <v>0.033</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2557</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.87</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1732</v>
+        <v>-0.1537</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.0228</v>
+        <v>-4.4573</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.3302</v>
+        <v>-4.756</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.79</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2547</v>
+        <v>-0.2351</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.3863</v>
+        <v>-6.8179</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5584</v>
+        <v>0.5362</v>
       </c>
       <c r="J42" t="n">
-        <v>13.96</v>
+        <v>13.405</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.92</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1161</v>
+        <v>-0.1003</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.9025</v>
+        <v>-2.5075</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.91</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1277</v>
+        <v>-0.1112</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.1925</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.8</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2422</v>
+        <v>-0.2226</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.055</v>
+        <v>-5.565</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4713</v>
+        <v>-0.4679</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.7825</v>
+        <v>-11.6975</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.48</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9218</v>
+        <v>0.9074</v>
       </c>
       <c r="J47" t="n">
-        <v>23.045</v>
+        <v>22.685</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.41</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8246</v>
+        <v>0.8096</v>
       </c>
       <c r="J48" t="n">
-        <v>20.615</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4982</v>
+        <v>0.4859</v>
       </c>
       <c r="J49" t="n">
-        <v>12.455</v>
+        <v>12.1475</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4466</v>
+        <v>0.4182</v>
       </c>
       <c r="J50" t="n">
-        <v>11.165</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.95</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2439</v>
+        <v>-0.2079</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.0975</v>
+        <v>-5.1975</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.63</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3056</v>
+        <v>-0.2866</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.1952</v>
+        <v>-4.8722</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.39</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5425</v>
+        <v>-0.5492</v>
       </c>
       <c r="J53" t="n">
-        <v>-9.2225</v>
+        <v>-9.336399999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.37</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5598</v>
+        <v>-0.5672</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.5166</v>
+        <v>-9.6424</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.33</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5961</v>
+        <v>-0.6063</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.1337</v>
+        <v>-10.3071</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.3</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6241</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.6097</v>
+        <v>-10.8392</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.27</v>
       </c>
       <c r="I57" t="n">
-        <v>1.7848</v>
+        <v>1.8295</v>
       </c>
       <c r="J57" t="n">
-        <v>30.3416</v>
+        <v>31.1015</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.77</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2258</v>
+        <v>1.2301</v>
       </c>
       <c r="J58" t="n">
-        <v>20.8386</v>
+        <v>20.9117</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.66</v>
       </c>
       <c r="I59" t="n">
-        <v>1.0985</v>
+        <v>1.0993</v>
       </c>
       <c r="J59" t="n">
-        <v>18.6745</v>
+        <v>18.6881</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.47</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8597</v>
+        <v>0.8565</v>
       </c>
       <c r="J60" t="n">
-        <v>14.6149</v>
+        <v>14.5605</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.36</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7089</v>
+        <v>0.7053</v>
       </c>
       <c r="J61" t="n">
-        <v>12.0513</v>
+        <v>11.9901</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.77</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7285</v>
       </c>
       <c r="J62" t="n">
-        <v>19.4175</v>
+        <v>18.2125</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2268</v>
+        <v>0.1823</v>
       </c>
       <c r="J63" t="n">
-        <v>5.67</v>
+        <v>4.5575</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.09</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1579</v>
+        <v>0.1231</v>
       </c>
       <c r="J64" t="n">
-        <v>3.9475</v>
+        <v>3.0775</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.95</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1001</v>
+        <v>-0.0832</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.5025</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1258</v>
+        <v>-0.1074</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.145</v>
+        <v>-2.685</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2982</v>
+        <v>0.2865</v>
       </c>
       <c r="J67" t="n">
-        <v>7.455</v>
+        <v>7.1625</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0069</v>
+        <v>0.0048</v>
       </c>
       <c r="J68" t="n">
-        <v>0.1725</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.3675</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2361</v>
+        <v>-0.216</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9025</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.75</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2945</v>
+        <v>-0.2762</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.3625</v>
+        <v>-6.905</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5664</v>
+        <v>0.5514</v>
       </c>
       <c r="J72" t="n">
-        <v>13.0272</v>
+        <v>12.6822</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.3082</v>
+        <v>-0.2916</v>
       </c>
       <c r="J73" t="n">
-        <v>-7.0886</v>
+        <v>-6.7068</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.72</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3082</v>
+        <v>-0.2916</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.0886</v>
+        <v>-6.7068</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3358</v>
+        <v>-0.3202</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.7234</v>
+        <v>-7.3646</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.57</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4436</v>
+        <v>-0.436</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.2028</v>
+        <v>-10.028</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.53</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9949</v>
+        <v>0.9821</v>
       </c>
       <c r="J77" t="n">
-        <v>22.8827</v>
+        <v>22.5883</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8709</v>
+        <v>0.8556</v>
       </c>
       <c r="J78" t="n">
-        <v>20.0307</v>
+        <v>19.6788</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2543</v>
+        <v>0.2236</v>
       </c>
       <c r="J79" t="n">
-        <v>5.8489</v>
+        <v>5.1428</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2263</v>
+        <v>0.1968</v>
       </c>
       <c r="J80" t="n">
-        <v>5.2049</v>
+        <v>4.5264</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.95</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2397</v>
+        <v>-0.2034</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.5131</v>
+        <v>-4.6782</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.15</v>
       </c>
       <c r="I82" t="n">
-        <v>0.368</v>
+        <v>0.3142</v>
       </c>
       <c r="J82" t="n">
-        <v>9.199999999999999</v>
+        <v>7.855</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0186</v>
+        <v>-0.0137</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.465</v>
+        <v>-0.3425</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2242</v>
+        <v>-0.2042</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.605</v>
+        <v>-5.105</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2342</v>
+        <v>-0.2143</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.855</v>
+        <v>-5.3575</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.254</v>
+        <v>-0.2343</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.35</v>
+        <v>-5.8575</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.38</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7824</v>
+        <v>0.7677</v>
       </c>
       <c r="J87" t="n">
-        <v>19.56</v>
+        <v>19.1925</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.33</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7104</v>
+        <v>0.6972</v>
       </c>
       <c r="J88" t="n">
-        <v>17.76</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.32</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6958</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>17.395</v>
+        <v>17.075</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.18</v>
       </c>
       <c r="I90" t="n">
-        <v>0.482</v>
+        <v>0.4643</v>
       </c>
       <c r="J90" t="n">
-        <v>12.05</v>
+        <v>11.6075</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1778</v>
+        <v>-0.1468</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.445</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.35</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8686</v>
+        <v>0.8477</v>
       </c>
       <c r="J92" t="n">
-        <v>24.3208</v>
+        <v>23.7356</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7255</v>
+        <v>0.6946</v>
       </c>
       <c r="J93" t="n">
-        <v>20.314</v>
+        <v>19.4488</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5538</v>
+        <v>0.5165</v>
       </c>
       <c r="J94" t="n">
-        <v>15.5064</v>
+        <v>14.462</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J95" t="n">
-        <v>4.1692</v>
+        <v>3.4748</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5911</v>
+        <v>-0.5538</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.5508</v>
+        <v>-15.5064</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2182</v>
+        <v>0.1748</v>
       </c>
       <c r="J97" t="n">
-        <v>6.1096</v>
+        <v>4.8944</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.05</v>
       </c>
       <c r="I98" t="n">
-        <v>0.153</v>
+        <v>0.1176</v>
       </c>
       <c r="J98" t="n">
-        <v>4.284</v>
+        <v>3.2928</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1046</v>
+        <v>0.0769</v>
       </c>
       <c r="J99" t="n">
-        <v>2.9288</v>
+        <v>2.1532</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.88</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1665</v>
+        <v>-0.1465</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.662</v>
+        <v>-4.102</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2495</v>
+        <v>-0.2295</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.986</v>
+        <v>-6.426</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.12</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4292</v>
+        <v>0.3879</v>
       </c>
       <c r="J102" t="n">
-        <v>15.4512</v>
+        <v>13.9644</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0225</v>
+        <v>0.0172</v>
       </c>
       <c r="J103" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6192</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.84</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4702</v>
+        <v>-0.4302</v>
       </c>
       <c r="J104" t="n">
-        <v>-16.9272</v>
+        <v>-15.4872</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5173</v>
+        <v>-0.4775</v>
       </c>
       <c r="J105" t="n">
-        <v>-18.6228</v>
+        <v>-17.19</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.68</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8279</v>
+        <v>-0.8036</v>
       </c>
       <c r="J106" t="n">
-        <v>-29.8044</v>
+        <v>-28.9296</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.7</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0804</v>
+        <v>1.0591</v>
       </c>
       <c r="J107" t="n">
-        <v>38.8944</v>
+        <v>38.1276</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.23</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4491</v>
+        <v>0.395</v>
       </c>
       <c r="J108" t="n">
-        <v>16.1676</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.16</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3371</v>
+        <v>0.2896</v>
       </c>
       <c r="J109" t="n">
-        <v>12.1356</v>
+        <v>10.4256</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0403</v>
+        <v>-0.0309</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.4508</v>
+        <v>-1.1124</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.93</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1278</v>
+        <v>-0.1095</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.6008</v>
+        <v>-3.942</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.32</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8249</v>
+        <v>0.8003</v>
       </c>
       <c r="J112" t="n">
-        <v>24.747</v>
+        <v>24.009</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.24</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6551</v>
+        <v>0.6192</v>
       </c>
       <c r="J113" t="n">
-        <v>19.653</v>
+        <v>18.576</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.1</v>
       </c>
       <c r="I114" t="n">
-        <v>0.327</v>
+        <v>0.2885</v>
       </c>
       <c r="J114" t="n">
-        <v>9.81</v>
+        <v>8.654999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.08</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2746</v>
+        <v>0.2387</v>
       </c>
       <c r="J115" t="n">
-        <v>8.238</v>
+        <v>7.161</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9495</v>
+        <v>-0.9415</v>
       </c>
       <c r="J116" t="n">
-        <v>-28.485</v>
+        <v>-28.245</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.31</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.5526</v>
       </c>
       <c r="J117" t="n">
-        <v>18.342</v>
+        <v>16.578</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.19</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4152</v>
+        <v>0.3583</v>
       </c>
       <c r="J118" t="n">
-        <v>12.456</v>
+        <v>10.749</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.03</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0993</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>2.979</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.77</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2823</v>
+        <v>-0.2636</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.468999999999999</v>
+        <v>-7.908</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.73</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3204</v>
+        <v>-0.3037</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.612</v>
+        <v>-9.111000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.52</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1073</v>
+        <v>1.1202</v>
       </c>
       <c r="J122" t="n">
-        <v>27.6825</v>
+        <v>28.005</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.47</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0388</v>
+        <v>1.0451</v>
       </c>
       <c r="J123" t="n">
-        <v>25.97</v>
+        <v>26.1275</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.42</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9595</v>
+        <v>0.954</v>
       </c>
       <c r="J124" t="n">
-        <v>23.9875</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.26</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6558</v>
+        <v>0.6309</v>
       </c>
       <c r="J125" t="n">
-        <v>16.395</v>
+        <v>15.7725</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.98</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1566</v>
+        <v>-0.1314</v>
       </c>
       <c r="J126" t="n">
-        <v>-3.915</v>
+        <v>-3.285</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5029</v>
+        <v>0.4555</v>
       </c>
       <c r="J127" t="n">
-        <v>12.5725</v>
+        <v>11.3875</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.82</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2148</v>
+        <v>-0.1978</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.37</v>
+        <v>-4.945</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.78</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2527</v>
+        <v>-0.2352</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.3175</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.61</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4086</v>
+        <v>-0.3977</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.215</v>
+        <v>-9.942500000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.57</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.444</v>
+        <v>-0.4366</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.1</v>
+        <v>-10.915</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.47</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0519</v>
+        <v>1.0582</v>
       </c>
       <c r="J132" t="n">
-        <v>29.4532</v>
+        <v>29.6296</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8424</v>
+        <v>0.8228</v>
       </c>
       <c r="J133" t="n">
-        <v>23.5872</v>
+        <v>23.0384</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6643</v>
+        <v>0.6359</v>
       </c>
       <c r="J134" t="n">
-        <v>18.6004</v>
+        <v>17.8052</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.15</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4258</v>
+        <v>0.393</v>
       </c>
       <c r="J135" t="n">
-        <v>11.9224</v>
+        <v>11.004</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.03</v>
       </c>
       <c r="I136" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>2.6656</v>
+        <v>2.0944</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.21</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4702</v>
+        <v>0.4133</v>
       </c>
       <c r="J137" t="n">
-        <v>13.1656</v>
+        <v>11.5724</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1836</v>
+        <v>0.144</v>
       </c>
       <c r="J138" t="n">
-        <v>5.1408</v>
+        <v>4.032</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1631</v>
+        <v>-0.1438</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.5668</v>
+        <v>-4.0264</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2457</v>
+        <v>-0.2258</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.8796</v>
+        <v>-6.3224</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3502</v>
+        <v>-0.3351</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.8056</v>
+        <v>-9.3828</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.29</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7275</v>
+        <v>0.7005</v>
       </c>
       <c r="J142" t="n">
-        <v>19.6425</v>
+        <v>18.9135</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.28</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7074</v>
+        <v>0.6794</v>
       </c>
       <c r="J143" t="n">
-        <v>19.0998</v>
+        <v>18.3438</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.24</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6258</v>
+        <v>0.5951</v>
       </c>
       <c r="J144" t="n">
-        <v>16.8966</v>
+        <v>16.0677</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.19</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5204</v>
+        <v>0.4874</v>
       </c>
       <c r="J145" t="n">
-        <v>14.0508</v>
+        <v>13.1598</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.15</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4292</v>
+        <v>0.3957</v>
       </c>
       <c r="J146" t="n">
-        <v>11.5884</v>
+        <v>10.6839</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.36</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7317</v>
+        <v>0.6843</v>
       </c>
       <c r="J147" t="n">
-        <v>19.7559</v>
+        <v>18.4761</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.9</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1387</v>
+        <v>-0.1216</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.7449</v>
+        <v>-3.2832</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.85</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1915</v>
+        <v>-0.1722</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.1705</v>
+        <v>-4.6494</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.68</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3554</v>
+        <v>-0.3405</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.595800000000001</v>
+        <v>-9.1935</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3826</v>
+        <v>-0.3698</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.3302</v>
+        <v>-9.9846</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.15</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3765</v>
+        <v>0.3234</v>
       </c>
       <c r="J152" t="n">
-        <v>11.295</v>
+        <v>9.702</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.09</v>
       </c>
       <c r="I153" t="n">
-        <v>0.259</v>
+        <v>0.2126</v>
       </c>
       <c r="J153" t="n">
-        <v>7.77</v>
+        <v>6.378</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1271</v>
+        <v>-0.1108</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.813</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.73</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3086</v>
+        <v>-0.291</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.257999999999999</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.54</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4793</v>
+        <v>-0.4767</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.379</v>
+        <v>-14.301</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.22</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5962</v>
+        <v>0.5602</v>
       </c>
       <c r="J157" t="n">
-        <v>17.886</v>
+        <v>16.806</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5744</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>17.232</v>
+        <v>16.134</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.19</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5303</v>
+        <v>0.493</v>
       </c>
       <c r="J159" t="n">
-        <v>15.909</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4627</v>
+        <v>0.4252</v>
       </c>
       <c r="J160" t="n">
-        <v>13.881</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2577</v>
+        <v>-0.2188</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.731</v>
+        <v>-6.564</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.25</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4585</v>
       </c>
       <c r="J162" t="n">
-        <v>15.0104</v>
+        <v>13.2965</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.468</v>
+        <v>0.4096</v>
       </c>
       <c r="J163" t="n">
-        <v>13.572</v>
+        <v>11.8784</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0251</v>
+        <v>-0.0181</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.7279</v>
+        <v>-0.5249</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2621</v>
+        <v>-0.2425</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.6009</v>
+        <v>-7.0325</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3102</v>
+        <v>-0.2929</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.995799999999999</v>
+        <v>-8.4941</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1515</v>
+        <v>1.1659</v>
       </c>
       <c r="J167" t="n">
-        <v>33.3935</v>
+        <v>33.8111</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.21</v>
       </c>
       <c r="I168" t="n">
-        <v>0.579</v>
+        <v>0.5415</v>
       </c>
       <c r="J168" t="n">
-        <v>16.791</v>
+        <v>15.7035</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.213</v>
+        <v>0.1828</v>
       </c>
       <c r="J169" t="n">
-        <v>6.177</v>
+        <v>5.3012</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.01</v>
       </c>
       <c r="I170" t="n">
-        <v>0.0404</v>
+        <v>0.0298</v>
       </c>
       <c r="J170" t="n">
-        <v>1.1716</v>
+        <v>0.8642</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6113</v>
+        <v>-0.5747</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.7277</v>
+        <v>-16.6663</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.097</v>
+        <v>1.1088</v>
       </c>
       <c r="J172" t="n">
-        <v>64.723</v>
+        <v>65.4192</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2971</v>
+        <v>0.2619</v>
       </c>
       <c r="J173" t="n">
-        <v>17.5289</v>
+        <v>15.4521</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.02</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0828</v>
+        <v>0.0654</v>
       </c>
       <c r="J174" t="n">
-        <v>4.8852</v>
+        <v>3.8586</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0182</v>
+        <v>-0.0133</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.0738</v>
+        <v>-0.7847</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1193</v>
+        <v>-0.0924</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.0387</v>
+        <v>-5.4516</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.27</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5438</v>
+        <v>0.4843</v>
       </c>
       <c r="J177" t="n">
-        <v>32.0842</v>
+        <v>28.5737</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.08</v>
       </c>
       <c r="I178" t="n">
-        <v>0.209</v>
+        <v>0.1675</v>
       </c>
       <c r="J178" t="n">
-        <v>12.331</v>
+        <v>9.8825</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0417</v>
+        <v>0.0287</v>
       </c>
       <c r="J179" t="n">
-        <v>2.4603</v>
+        <v>1.6933</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0266</v>
+        <v>-0.0189</v>
       </c>
       <c r="J180" t="n">
-        <v>-1.5694</v>
+        <v>-1.1151</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2934</v>
+        <v>-0.2752</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.3106</v>
+        <v>-16.2368</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.4</v>
       </c>
       <c r="I182" t="n">
-        <v>0.802</v>
+        <v>0.7613</v>
       </c>
       <c r="J182" t="n">
-        <v>20.852</v>
+        <v>19.7938</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.03</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1246</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>3.2396</v>
+        <v>2.4518</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.93</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1021</v>
+        <v>-0.0877</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.6546</v>
+        <v>-2.2802</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4954</v>
+        <v>-0.4948</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.8804</v>
+        <v>-12.8648</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.48</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.7722</v>
+        <v>-13.8788</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.67</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3258</v>
+        <v>1.3474</v>
       </c>
       <c r="J187" t="n">
-        <v>34.4708</v>
+        <v>35.0324</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.25</v>
       </c>
       <c r="I188" t="n">
-        <v>0.647</v>
+        <v>0.6165</v>
       </c>
       <c r="J188" t="n">
-        <v>16.822</v>
+        <v>16.029</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3574</v>
+        <v>0.3242</v>
       </c>
       <c r="J189" t="n">
-        <v>9.292400000000001</v>
+        <v>8.4292</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2799</v>
+        <v>0.2484</v>
       </c>
       <c r="J190" t="n">
-        <v>7.2774</v>
+        <v>6.4584</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.99</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J191" t="n">
-        <v>-2.5376</v>
+        <v>-1.9968</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.28</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.6983</v>
       </c>
       <c r="J192" t="n">
-        <v>20.4204</v>
+        <v>19.5524</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.26</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6871</v>
+        <v>0.6538</v>
       </c>
       <c r="J193" t="n">
-        <v>19.2388</v>
+        <v>18.3064</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.23</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6227</v>
+        <v>0.5866</v>
       </c>
       <c r="J194" t="n">
-        <v>17.4356</v>
+        <v>16.4248</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.2</v>
       </c>
       <c r="I195" t="n">
-        <v>0.5568</v>
+        <v>0.5188</v>
       </c>
       <c r="J195" t="n">
-        <v>15.5904</v>
+        <v>14.5264</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.63</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9774</v>
+        <v>-0.9741</v>
       </c>
       <c r="J196" t="n">
-        <v>-27.3672</v>
+        <v>-27.2748</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.2</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4396</v>
+        <v>0.3821</v>
       </c>
       <c r="J197" t="n">
-        <v>12.3088</v>
+        <v>10.6988</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3695</v>
+        <v>0.3146</v>
       </c>
       <c r="J198" t="n">
-        <v>10.346</v>
+        <v>8.8088</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0809</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.7216</v>
+        <v>-2.2652</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.87</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1781</v>
+        <v>-0.1578</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.9868</v>
+        <v>-4.4184</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3363</v>
+        <v>-0.3205</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.416399999999999</v>
+        <v>-8.974</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.83</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.1995</v>
+        <v>-0.1837</v>
       </c>
       <c r="J202" t="n">
-        <v>-4.389</v>
+        <v>-4.0414</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.83</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1995</v>
+        <v>-0.1837</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.389</v>
+        <v>-4.0414</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.77</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2589</v>
+        <v>-0.243</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.6958</v>
+        <v>-5.346</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.277</v>
+        <v>-0.2611</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.094</v>
+        <v>-5.7442</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.58</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4301</v>
+        <v>-0.4211</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.462199999999999</v>
+        <v>-9.264200000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.61</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2269</v>
+        <v>1.2429</v>
       </c>
       <c r="J207" t="n">
-        <v>26.9918</v>
+        <v>27.3438</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.44</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9944</v>
+        <v>0.9936</v>
       </c>
       <c r="J208" t="n">
-        <v>21.8768</v>
+        <v>21.8592</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.38</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8887</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>19.5514</v>
+        <v>19.261</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4619</v>
+        <v>0.4309</v>
       </c>
       <c r="J210" t="n">
-        <v>10.1618</v>
+        <v>9.479799999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.0537</v>
+        <v>-0.0495</v>
       </c>
       <c r="J211" t="n">
-        <v>-1.1814</v>
+        <v>-1.089</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.26</v>
       </c>
       <c r="I212" t="n">
-        <v>0.535</v>
+        <v>0.4758</v>
       </c>
       <c r="J212" t="n">
-        <v>18.725</v>
+        <v>16.653</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.1</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2536</v>
+        <v>0.2069</v>
       </c>
       <c r="J213" t="n">
-        <v>8.875999999999999</v>
+        <v>7.2415</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.111</v>
+        <v>-0.0934</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.885</v>
+        <v>-3.269</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1464</v>
+        <v>-0.1269</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.124</v>
+        <v>-4.4415</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2715</v>
+        <v>-0.2523</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.5025</v>
+        <v>-8.830500000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.47</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0865</v>
+        <v>1.0977</v>
       </c>
       <c r="J217" t="n">
-        <v>38.0275</v>
+        <v>38.4195</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.446</v>
+        <v>0.4062</v>
       </c>
       <c r="J218" t="n">
-        <v>15.61</v>
+        <v>14.217</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1533</v>
+        <v>-0.1221</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.3655</v>
+        <v>-4.2735</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1871</v>
+        <v>-0.1526</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.5485</v>
+        <v>-5.341</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.95</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.219</v>
+        <v>-0.182</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.665</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.37</v>
       </c>
       <c r="I222" t="n">
-        <v>0.883</v>
+        <v>0.8659</v>
       </c>
       <c r="J222" t="n">
-        <v>22.075</v>
+        <v>21.6475</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.3</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7457</v>
+        <v>0.7201</v>
       </c>
       <c r="J223" t="n">
-        <v>18.6425</v>
+        <v>18.0025</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.22</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5836</v>
+        <v>0.5523</v>
       </c>
       <c r="J224" t="n">
-        <v>14.59</v>
+        <v>13.8075</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.18</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4964</v>
+        <v>0.4638</v>
       </c>
       <c r="J225" t="n">
-        <v>12.41</v>
+        <v>11.595</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4035</v>
+        <v>0.3704</v>
       </c>
       <c r="J226" t="n">
-        <v>10.0875</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.11</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3103</v>
+        <v>0.2618</v>
       </c>
       <c r="J227" t="n">
-        <v>7.7575</v>
+        <v>6.545</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.89</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1467</v>
+        <v>-0.1302</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.6675</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.78</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2576</v>
+        <v>-0.2388</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.44</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.77</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2672</v>
+        <v>-0.2486</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.68</v>
+        <v>-6.215</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.7</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.333</v>
+        <v>-0.3168</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.324999999999999</v>
+        <v>-7.92</v>
       </c>
     </row>
   </sheetData>
